--- a/research/traditional_assets/database/data/malaysia/malaysia_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_restaurant_dining.xlsx
@@ -1767,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1904,22 +1904,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.095885781845559</v>
+        <v>0.09572785596912965</v>
       </c>
       <c r="C2">
-        <v>40.86640569529136</v>
+        <v>40.57464742531971</v>
       </c>
       <c r="D2">
-        <v>38.64640569529136</v>
+        <v>38.76864742531971</v>
       </c>
       <c r="E2">
-        <v>-5.800000000000001</v>
+        <v>-5.386000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4140000000000001</v>
       </c>
       <c r="G2">
         <v>2.22</v>
@@ -1940,45 +1940,45 @@
         <v>0.114</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02289420000000001</v>
       </c>
       <c r="N2">
-        <v>0.114</v>
+        <v>0.0911058</v>
       </c>
       <c r="O2">
-        <v>0.02736</v>
+        <v>0.021865392</v>
       </c>
       <c r="P2">
-        <v>0.08664000000000001</v>
+        <v>0.069240408</v>
       </c>
       <c r="Q2">
-        <v>-0.02736</v>
+        <v>-0.044759592</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.095885781845559</v>
+        <v>0.09627027875669662</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326223</v>
+        <v>0.8510014065309738</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
+        <v>0.0553</v>
       </c>
       <c r="V2">
         <v>0.24</v>
       </c>
       <c r="W2">
-        <v>0.038228</v>
+        <v>0.042028</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>4.97942710380795</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1986,22 +1986,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09572785596912965</v>
+        <v>0.09609737009270031</v>
       </c>
       <c r="C3">
-        <v>40.57464742531971</v>
+        <v>39.87583009294261</v>
       </c>
       <c r="D3">
-        <v>38.76864742531971</v>
+        <v>38.48383009294261</v>
       </c>
       <c r="E3">
-        <v>-5.386000000000001</v>
+        <v>-4.972</v>
       </c>
       <c r="F3">
-        <v>0.4140000000000001</v>
+        <v>0.8280000000000002</v>
       </c>
       <c r="G3">
         <v>2.22</v>
@@ -2022,45 +2022,45 @@
         <v>0.114</v>
       </c>
       <c r="M3">
-        <v>0.02289420000000001</v>
+        <v>0.07452000000000002</v>
       </c>
       <c r="N3">
-        <v>0.0911058</v>
+        <v>0.03947999999999999</v>
       </c>
       <c r="O3">
-        <v>0.021865392</v>
+        <v>0.009475199999999996</v>
       </c>
       <c r="P3">
-        <v>0.069240408</v>
+        <v>0.03000479999999999</v>
       </c>
       <c r="Q3">
-        <v>-0.044759592</v>
+        <v>-0.08399520000000002</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09627027875669662</v>
+        <v>0.09666262254357175</v>
       </c>
       <c r="T3">
-        <v>0.8510014065309738</v>
+        <v>0.8576168864272508</v>
       </c>
       <c r="U3">
-        <v>0.0553</v>
+        <v>0.09</v>
       </c>
       <c r="V3">
         <v>0.24</v>
       </c>
       <c r="W3">
-        <v>0.042028</v>
+        <v>0.0684</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y3">
-        <v>4.97942710380795</v>
+        <v>1.529790660225443</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2068,22 +2068,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09609737009270031</v>
+        <v>0.1007845383665509</v>
       </c>
       <c r="C4">
-        <v>39.87583009294261</v>
+        <v>36.18126808721285</v>
       </c>
       <c r="D4">
-        <v>38.48383009294261</v>
+        <v>35.20326808721285</v>
       </c>
       <c r="E4">
-        <v>-4.972</v>
+        <v>-4.558000000000001</v>
       </c>
       <c r="F4">
-        <v>0.8280000000000002</v>
+        <v>1.242</v>
       </c>
       <c r="G4">
         <v>2.22</v>
@@ -2104,45 +2104,45 @@
         <v>0.114</v>
       </c>
       <c r="M4">
-        <v>0.07452000000000002</v>
+        <v>0.2928636000000001</v>
       </c>
       <c r="N4">
-        <v>0.03947999999999999</v>
+        <v>-0.1788636000000001</v>
       </c>
       <c r="O4">
-        <v>0.009475199999999996</v>
+        <v>-0.04292726400000001</v>
       </c>
       <c r="P4">
-        <v>0.03000479999999999</v>
+        <v>-0.135936336</v>
       </c>
       <c r="Q4">
-        <v>-0.08399520000000002</v>
+        <v>-0.249936336</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09666262254357175</v>
+        <v>0.09729011126986423</v>
       </c>
       <c r="T4">
-        <v>0.8576168864272508</v>
+        <v>0.8681972478164055</v>
       </c>
       <c r="U4">
-        <v>0.09</v>
+        <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>0.24</v>
+        <v>0.09342233039544687</v>
       </c>
       <c r="W4">
-        <v>0.0684</v>
+        <v>0.2137710144927536</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y4">
-        <v>1.529790660225443</v>
+        <v>0.3892597099810287</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2150,22 +2150,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1007845383665509</v>
+        <v>0.1026845383665509</v>
       </c>
       <c r="C5">
-        <v>36.18126808721285</v>
+        <v>34.59144401820652</v>
       </c>
       <c r="D5">
-        <v>35.20326808721285</v>
+        <v>34.02744401820652</v>
       </c>
       <c r="E5">
-        <v>-4.558000000000001</v>
+        <v>-4.144</v>
       </c>
       <c r="F5">
-        <v>1.242</v>
+        <v>1.656</v>
       </c>
       <c r="G5">
         <v>2.22</v>
@@ -2186,37 +2186,37 @@
         <v>0.114</v>
       </c>
       <c r="M5">
-        <v>0.2928636000000001</v>
+        <v>0.3904848000000001</v>
       </c>
       <c r="N5">
-        <v>-0.1788636000000001</v>
+        <v>-0.2764848000000001</v>
       </c>
       <c r="O5">
-        <v>-0.04292726400000001</v>
+        <v>-0.06635635200000002</v>
       </c>
       <c r="P5">
-        <v>-0.135936336</v>
+        <v>-0.2101284480000001</v>
       </c>
       <c r="Q5">
-        <v>-0.249936336</v>
+        <v>-0.3241284480000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09729011126986423</v>
+        <v>0.09782646659559198</v>
       </c>
       <c r="T5">
-        <v>0.8681972478164055</v>
+        <v>0.8772409691478263</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>0.09342233039544687</v>
+        <v>0.07006674779658516</v>
       </c>
       <c r="W5">
-        <v>0.2137710144927536</v>
+        <v>0.2192782608695652</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>0.3892597099810287</v>
+        <v>0.2919447824857715</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2232,22 +2232,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1026845383665509</v>
+        <v>0.1045845383665509</v>
       </c>
       <c r="C6">
-        <v>34.59144401820652</v>
+        <v>33.07762856620018</v>
       </c>
       <c r="D6">
-        <v>34.02744401820652</v>
+        <v>32.92762856620018</v>
       </c>
       <c r="E6">
-        <v>-4.144</v>
+        <v>-3.73</v>
       </c>
       <c r="F6">
-        <v>1.656</v>
+        <v>2.07</v>
       </c>
       <c r="G6">
         <v>2.22</v>
@@ -2268,37 +2268,37 @@
         <v>0.114</v>
       </c>
       <c r="M6">
-        <v>0.3904848000000001</v>
+        <v>0.4881060000000001</v>
       </c>
       <c r="N6">
-        <v>-0.2764848000000001</v>
+        <v>-0.3741060000000001</v>
       </c>
       <c r="O6">
-        <v>-0.06635635200000002</v>
+        <v>-0.08978544000000002</v>
       </c>
       <c r="P6">
-        <v>-0.2101284480000001</v>
+        <v>-0.2843205600000001</v>
       </c>
       <c r="Q6">
-        <v>-0.3241284480000001</v>
+        <v>-0.39832056</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09782646659559198</v>
+        <v>0.09837411361238768</v>
       </c>
       <c r="T6">
-        <v>0.8772409691478263</v>
+        <v>0.8864750846125403</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>0.07006674779658516</v>
+        <v>0.05605339823726812</v>
       </c>
       <c r="W6">
-        <v>0.2192782608695652</v>
+        <v>0.2225826086956522</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>0.2919447824857715</v>
+        <v>0.2335558259886171</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2314,22 +2314,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1045845383665509</v>
+        <v>0.1064845383665509</v>
       </c>
       <c r="C7">
-        <v>33.07762856620018</v>
+        <v>31.6326823654087</v>
       </c>
       <c r="D7">
-        <v>32.92762856620018</v>
+        <v>31.8966823654087</v>
       </c>
       <c r="E7">
-        <v>-3.73</v>
+        <v>-3.316</v>
       </c>
       <c r="F7">
-        <v>2.07</v>
+        <v>2.484</v>
       </c>
       <c r="G7">
         <v>2.22</v>
@@ -2350,37 +2350,37 @@
         <v>0.114</v>
       </c>
       <c r="M7">
-        <v>0.4881060000000001</v>
+        <v>0.5857272000000001</v>
       </c>
       <c r="N7">
-        <v>-0.3741060000000001</v>
+        <v>-0.4717272000000001</v>
       </c>
       <c r="O7">
-        <v>-0.08978544000000002</v>
+        <v>-0.113214528</v>
       </c>
       <c r="P7">
-        <v>-0.2843205600000001</v>
+        <v>-0.3585126720000001</v>
       </c>
       <c r="Q7">
-        <v>-0.39832056</v>
+        <v>-0.4725126720000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09837411361238768</v>
+        <v>0.09893341269337053</v>
       </c>
       <c r="T7">
-        <v>0.8864750846125403</v>
+        <v>0.8959056706190566</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>0.05605339823726812</v>
+        <v>0.04671116519772343</v>
       </c>
       <c r="W7">
-        <v>0.2225826086956522</v>
+        <v>0.2247855072463768</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>0.2335558259886171</v>
+        <v>0.1946298549905143</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2396,22 +2396,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1064845383665509</v>
+        <v>0.1083845383665509</v>
       </c>
       <c r="C8">
-        <v>31.6326823654087</v>
+        <v>30.25033302424511</v>
       </c>
       <c r="D8">
-        <v>31.8966823654087</v>
+        <v>30.92833302424511</v>
       </c>
       <c r="E8">
-        <v>-3.316</v>
+        <v>-2.902000000000001</v>
       </c>
       <c r="F8">
-        <v>2.484</v>
+        <v>2.898</v>
       </c>
       <c r="G8">
         <v>2.22</v>
@@ -2432,37 +2432,37 @@
         <v>0.114</v>
       </c>
       <c r="M8">
-        <v>0.5857272000000001</v>
+        <v>0.6833484000000001</v>
       </c>
       <c r="N8">
-        <v>-0.4717272000000001</v>
+        <v>-0.5693484000000001</v>
       </c>
       <c r="O8">
-        <v>-0.113214528</v>
+        <v>-0.136643616</v>
       </c>
       <c r="P8">
-        <v>-0.3585126720000001</v>
+        <v>-0.4327047840000001</v>
       </c>
       <c r="Q8">
-        <v>-0.4725126720000001</v>
+        <v>-0.5467047840000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09893341269337053</v>
+        <v>0.09950473971157882</v>
       </c>
       <c r="T8">
-        <v>0.8959056706190566</v>
+        <v>0.9055390649267885</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>0.04671116519772343</v>
+        <v>0.04003814159804867</v>
       </c>
       <c r="W8">
-        <v>0.2247855072463768</v>
+        <v>0.2263590062111801</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>0.1946298549905143</v>
+        <v>0.1668255899918694</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2478,22 +2478,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1083845383665509</v>
+        <v>0.1102845383665509</v>
       </c>
       <c r="C9">
-        <v>30.25033302424512</v>
+        <v>28.92504740082896</v>
       </c>
       <c r="D9">
-        <v>30.92833302424512</v>
+        <v>30.01704740082896</v>
       </c>
       <c r="E9">
-        <v>-2.902</v>
+        <v>-2.488</v>
       </c>
       <c r="F9">
-        <v>2.898000000000001</v>
+        <v>3.312000000000001</v>
       </c>
       <c r="G9">
         <v>2.22</v>
@@ -2514,37 +2514,37 @@
         <v>0.114</v>
       </c>
       <c r="M9">
-        <v>0.6833484000000002</v>
+        <v>0.7809696000000002</v>
       </c>
       <c r="N9">
-        <v>-0.5693484000000002</v>
+        <v>-0.6669696000000002</v>
       </c>
       <c r="O9">
-        <v>-0.1366436160000001</v>
+        <v>-0.160072704</v>
       </c>
       <c r="P9">
-        <v>-0.4327047840000001</v>
+        <v>-0.5068968960000001</v>
       </c>
       <c r="Q9">
-        <v>-0.5467047840000001</v>
+        <v>-0.6208968960000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09950473971157882</v>
+        <v>0.1000884868823568</v>
       </c>
       <c r="T9">
-        <v>0.9055390649267885</v>
+        <v>0.9153818808499056</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>0.04003814159804866</v>
+        <v>0.03503337389829258</v>
       </c>
       <c r="W9">
-        <v>0.2263590062111801</v>
+        <v>0.2275391304347826</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>0.1668255899918694</v>
+        <v>0.1459723912428857</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2560,22 +2560,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1102845383665509</v>
+        <v>0.1121845383665509</v>
       </c>
       <c r="C10">
-        <v>28.92504740082896</v>
+        <v>27.65192581220446</v>
       </c>
       <c r="D10">
-        <v>30.01704740082896</v>
+        <v>29.15792581220446</v>
       </c>
       <c r="E10">
-        <v>-2.488</v>
+        <v>-2.074</v>
       </c>
       <c r="F10">
-        <v>3.312000000000001</v>
+        <v>3.726</v>
       </c>
       <c r="G10">
         <v>2.22</v>
@@ -2596,37 +2596,37 @@
         <v>0.114</v>
       </c>
       <c r="M10">
-        <v>0.7809696000000002</v>
+        <v>0.8785908000000001</v>
       </c>
       <c r="N10">
-        <v>-0.6669696000000002</v>
+        <v>-0.7645908000000001</v>
       </c>
       <c r="O10">
-        <v>-0.160072704</v>
+        <v>-0.183501792</v>
       </c>
       <c r="P10">
-        <v>-0.5068968960000001</v>
+        <v>-0.5810890080000001</v>
       </c>
       <c r="Q10">
-        <v>-0.6208968960000001</v>
+        <v>-0.6950890080000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1000884868823568</v>
+        <v>0.1006850636612839</v>
       </c>
       <c r="T10">
-        <v>0.9153818808499056</v>
+        <v>0.9254410223977069</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>0.03503337389829258</v>
+        <v>0.03114077679848229</v>
       </c>
       <c r="W10">
-        <v>0.2275391304347826</v>
+        <v>0.2284570048309179</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>0.1459723912428857</v>
+        <v>0.1297532366603429</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2642,22 +2642,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1121845383665509</v>
+        <v>0.1140845383665509</v>
       </c>
       <c r="C11">
-        <v>27.65192581220446</v>
+        <v>26.42661390516921</v>
       </c>
       <c r="D11">
-        <v>29.15792581220446</v>
+        <v>28.34661390516921</v>
       </c>
       <c r="E11">
-        <v>-2.074</v>
+        <v>-1.66</v>
       </c>
       <c r="F11">
-        <v>3.726</v>
+        <v>4.140000000000001</v>
       </c>
       <c r="G11">
         <v>2.22</v>
@@ -2678,37 +2678,37 @@
         <v>0.114</v>
       </c>
       <c r="M11">
-        <v>0.8785908000000001</v>
+        <v>0.9762120000000002</v>
       </c>
       <c r="N11">
-        <v>-0.7645908000000001</v>
+        <v>-0.8622120000000002</v>
       </c>
       <c r="O11">
-        <v>-0.183501792</v>
+        <v>-0.20693088</v>
       </c>
       <c r="P11">
-        <v>-0.5810890080000001</v>
+        <v>-0.6552811200000002</v>
       </c>
       <c r="Q11">
-        <v>-0.6950890080000001</v>
+        <v>-0.7692811200000002</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1006850636612839</v>
+        <v>0.1012948977019648</v>
       </c>
       <c r="T11">
-        <v>0.9254410223977069</v>
+        <v>0.9357237004243479</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>0.03114077679848229</v>
+        <v>0.02802669911863406</v>
       </c>
       <c r="W11">
-        <v>0.2284570048309179</v>
+        <v>0.2291913043478261</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>0.1297532366603429</v>
+        <v>0.1167779129943086</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2724,22 +2724,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1140845383665509</v>
+        <v>0.1159845383665509</v>
       </c>
       <c r="C12">
-        <v>26.4266139051692</v>
+        <v>25.24522884183038</v>
       </c>
       <c r="D12">
-        <v>28.3466139051692</v>
+        <v>27.57922884183039</v>
       </c>
       <c r="E12">
-        <v>-1.66</v>
+        <v>-1.246</v>
       </c>
       <c r="F12">
-        <v>4.140000000000001</v>
+        <v>4.554</v>
       </c>
       <c r="G12">
         <v>2.22</v>
@@ -2760,37 +2760,37 @@
         <v>0.114</v>
       </c>
       <c r="M12">
-        <v>0.9762120000000002</v>
+        <v>1.0738332</v>
       </c>
       <c r="N12">
-        <v>-0.8622120000000002</v>
+        <v>-0.9598332000000002</v>
       </c>
       <c r="O12">
-        <v>-0.20693088</v>
+        <v>-0.230359968</v>
       </c>
       <c r="P12">
-        <v>-0.6552811200000002</v>
+        <v>-0.7294732320000001</v>
       </c>
       <c r="Q12">
-        <v>-0.7692811200000002</v>
+        <v>-0.8434732320000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1012948977019648</v>
+        <v>0.1019184358783913</v>
       </c>
       <c r="T12">
-        <v>0.9357237004243482</v>
+        <v>0.9462374498673183</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>0.02802669911863406</v>
+        <v>0.02547881738057642</v>
       </c>
       <c r="W12">
-        <v>0.2291913043478261</v>
+        <v>0.2297920948616601</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>0.1167779129943086</v>
+        <v>0.1061617390857351</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2806,22 +2806,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1159845383665509</v>
+        <v>0.1178845383665509</v>
       </c>
       <c r="C13">
-        <v>25.24522884183038</v>
+        <v>24.10429715874156</v>
       </c>
       <c r="D13">
-        <v>27.57922884183039</v>
+        <v>26.85229715874156</v>
       </c>
       <c r="E13">
-        <v>-1.246</v>
+        <v>-0.8319999999999999</v>
       </c>
       <c r="F13">
-        <v>4.554</v>
+        <v>4.968000000000001</v>
       </c>
       <c r="G13">
         <v>2.22</v>
@@ -2842,37 +2842,37 @@
         <v>0.114</v>
       </c>
       <c r="M13">
-        <v>1.0738332</v>
+        <v>1.1714544</v>
       </c>
       <c r="N13">
-        <v>-0.9598332000000002</v>
+        <v>-1.0574544</v>
       </c>
       <c r="O13">
-        <v>-0.230359968</v>
+        <v>-0.253789056</v>
       </c>
       <c r="P13">
-        <v>-0.7294732320000001</v>
+        <v>-0.8036653440000001</v>
       </c>
       <c r="Q13">
-        <v>-0.8434732320000001</v>
+        <v>-0.9176653440000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1019184358783913</v>
+        <v>0.1025561453770094</v>
       </c>
       <c r="T13">
-        <v>0.9462374498673183</v>
+        <v>0.956990148161265</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>0.02547881738057642</v>
+        <v>0.02335558259886172</v>
       </c>
       <c r="W13">
-        <v>0.2297920948616601</v>
+        <v>0.2302927536231884</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.1061617390857351</v>
+        <v>0.09731492749525728</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2888,22 +2888,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1178845383665509</v>
+        <v>0.1197845383665509</v>
       </c>
       <c r="C14">
-        <v>24.10429715874156</v>
+        <v>23.00070220109193</v>
       </c>
       <c r="D14">
-        <v>26.85229715874156</v>
+        <v>26.16270220109194</v>
       </c>
       <c r="E14">
-        <v>-0.8319999999999999</v>
+        <v>-0.4180000000000001</v>
       </c>
       <c r="F14">
-        <v>4.968000000000001</v>
+        <v>5.382000000000001</v>
       </c>
       <c r="G14">
         <v>2.22</v>
@@ -2924,37 +2924,37 @@
         <v>0.114</v>
       </c>
       <c r="M14">
-        <v>1.1714544</v>
+        <v>1.2690756</v>
       </c>
       <c r="N14">
-        <v>-1.0574544</v>
+        <v>-1.1550756</v>
       </c>
       <c r="O14">
-        <v>-0.253789056</v>
+        <v>-0.277218144</v>
       </c>
       <c r="P14">
-        <v>-0.8036653440000001</v>
+        <v>-0.877857456</v>
       </c>
       <c r="Q14">
-        <v>-0.9176653440000001</v>
+        <v>-0.991857456</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1025561453770094</v>
+        <v>0.1032085148641015</v>
       </c>
       <c r="T14">
-        <v>0.956990148161265</v>
+        <v>0.9679900349217393</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.02335558259886172</v>
+        <v>0.0215589993220262</v>
       </c>
       <c r="W14">
-        <v>0.2302927536231884</v>
+        <v>0.2307163879598662</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>0.09731492749525728</v>
+        <v>0.08982916384177597</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2970,22 +2970,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1197845383665509</v>
+        <v>0.1216845383665509</v>
       </c>
       <c r="C15">
-        <v>23.00070220109193</v>
+        <v>21.93163945376439</v>
       </c>
       <c r="D15">
-        <v>26.16270220109194</v>
+        <v>25.50763945376439</v>
       </c>
       <c r="E15">
-        <v>-0.4180000000000001</v>
+        <v>-0.003999999999999559</v>
       </c>
       <c r="F15">
-        <v>5.382000000000001</v>
+        <v>5.796000000000001</v>
       </c>
       <c r="G15">
         <v>2.22</v>
@@ -3006,37 +3006,37 @@
         <v>0.114</v>
       </c>
       <c r="M15">
-        <v>1.2690756</v>
+        <v>1.3666968</v>
       </c>
       <c r="N15">
-        <v>-1.1550756</v>
+        <v>-1.2526968</v>
       </c>
       <c r="O15">
-        <v>-0.277218144</v>
+        <v>-0.300647232</v>
       </c>
       <c r="P15">
-        <v>-0.877857456</v>
+        <v>-0.9520495680000003</v>
       </c>
       <c r="Q15">
-        <v>-0.991857456</v>
+        <v>-1.066049568</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1032085148641015</v>
+        <v>0.1038760557346143</v>
       </c>
       <c r="T15">
-        <v>0.9679900349217393</v>
+        <v>0.9792457330022247</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.0215589993220262</v>
+        <v>0.02001907079902433</v>
       </c>
       <c r="W15">
-        <v>0.2307163879598662</v>
+        <v>0.2310795031055901</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.08982916384177597</v>
+        <v>0.08341279499593479</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3052,22 +3052,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1216845383665509</v>
+        <v>0.1235845383665509</v>
       </c>
       <c r="C16">
-        <v>21.93163945376439</v>
+        <v>20.89457841901519</v>
       </c>
       <c r="D16">
-        <v>25.50763945376439</v>
+        <v>24.88457841901519</v>
       </c>
       <c r="E16">
-        <v>-0.003999999999999559</v>
+        <v>0.410000000000001</v>
       </c>
       <c r="F16">
-        <v>5.796000000000001</v>
+        <v>6.210000000000002</v>
       </c>
       <c r="G16">
         <v>2.22</v>
@@ -3088,37 +3088,37 @@
         <v>0.114</v>
       </c>
       <c r="M16">
-        <v>1.3666968</v>
+        <v>1.464318</v>
       </c>
       <c r="N16">
-        <v>-1.2526968</v>
+        <v>-1.350318</v>
       </c>
       <c r="O16">
-        <v>-0.300647232</v>
+        <v>-0.3240763200000001</v>
       </c>
       <c r="P16">
-        <v>-0.9520495680000003</v>
+        <v>-1.02624168</v>
       </c>
       <c r="Q16">
-        <v>-1.066049568</v>
+        <v>-1.14024168</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1038760557346143</v>
+        <v>0.1045593034491392</v>
       </c>
       <c r="T16">
-        <v>0.9792457330022247</v>
+        <v>0.9907662710375451</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.02001907079902433</v>
+        <v>0.01868446607908937</v>
       </c>
       <c r="W16">
-        <v>0.2310795031055901</v>
+        <v>0.2313942028985507</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.08341279499593479</v>
+        <v>0.07785194199620582</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3134,22 +3134,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1235845383665509</v>
+        <v>0.1254845383665509</v>
       </c>
       <c r="C17">
-        <v>20.89457841901519</v>
+        <v>19.88722994809055</v>
       </c>
       <c r="D17">
-        <v>24.8845784190152</v>
+        <v>24.29122994809055</v>
       </c>
       <c r="E17">
-        <v>0.4100000000000001</v>
+        <v>0.8240000000000007</v>
       </c>
       <c r="F17">
-        <v>6.210000000000001</v>
+        <v>6.624000000000001</v>
       </c>
       <c r="G17">
         <v>2.22</v>
@@ -3170,37 +3170,37 @@
         <v>0.114</v>
       </c>
       <c r="M17">
-        <v>1.464318</v>
+        <v>1.5619392</v>
       </c>
       <c r="N17">
-        <v>-1.350318</v>
+        <v>-1.4479392</v>
       </c>
       <c r="O17">
-        <v>-0.32407632</v>
+        <v>-0.347505408</v>
       </c>
       <c r="P17">
-        <v>-1.02624168</v>
+        <v>-1.100433792</v>
       </c>
       <c r="Q17">
-        <v>-1.14024168</v>
+        <v>-1.214433792</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1045593034491392</v>
+        <v>0.1052588189663908</v>
       </c>
       <c r="T17">
-        <v>0.9907662710375449</v>
+        <v>1.002561107597516</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.01868446607908938</v>
+        <v>0.01751668694914629</v>
       </c>
       <c r="W17">
-        <v>0.2313942028985507</v>
+        <v>0.2316695652173913</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.07785194199620582</v>
+        <v>0.07298619562144293</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3216,22 +3216,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1254845383665509</v>
+        <v>0.1273845383665509</v>
       </c>
       <c r="C18">
-        <v>19.88722994809055</v>
+        <v>18.90751813767361</v>
       </c>
       <c r="D18">
-        <v>24.29122994809055</v>
+        <v>23.72551813767361</v>
       </c>
       <c r="E18">
-        <v>0.8240000000000007</v>
+        <v>1.238</v>
       </c>
       <c r="F18">
-        <v>6.624000000000001</v>
+        <v>7.038000000000001</v>
       </c>
       <c r="G18">
         <v>2.22</v>
@@ -3252,37 +3252,37 @@
         <v>0.114</v>
       </c>
       <c r="M18">
-        <v>1.5619392</v>
+        <v>1.6595604</v>
       </c>
       <c r="N18">
-        <v>-1.4479392</v>
+        <v>-1.5455604</v>
       </c>
       <c r="O18">
-        <v>-0.347505408</v>
+        <v>-0.3709344960000001</v>
       </c>
       <c r="P18">
-        <v>-1.100433792</v>
+        <v>-1.174625904</v>
       </c>
       <c r="Q18">
-        <v>-1.214433792</v>
+        <v>-1.288625904</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1052588189663908</v>
+        <v>0.1059751902792389</v>
       </c>
       <c r="T18">
-        <v>1.002561107597516</v>
+        <v>1.014640157086642</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.01751668694914629</v>
+        <v>0.01648629359919651</v>
       </c>
       <c r="W18">
-        <v>0.2316695652173913</v>
+        <v>0.2319125319693095</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.07298619562144293</v>
+        <v>0.06869288999665213</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3298,22 +3298,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1273845383665509</v>
+        <v>0.1292845383665509</v>
       </c>
       <c r="C19">
-        <v>18.90751813767361</v>
+        <v>17.95355606393419</v>
       </c>
       <c r="D19">
-        <v>23.72551813767361</v>
+        <v>23.1855560639342</v>
       </c>
       <c r="E19">
-        <v>1.238</v>
+        <v>1.652000000000001</v>
       </c>
       <c r="F19">
-        <v>7.038000000000001</v>
+        <v>7.452000000000002</v>
       </c>
       <c r="G19">
         <v>2.22</v>
@@ -3334,37 +3334,37 @@
         <v>0.114</v>
       </c>
       <c r="M19">
-        <v>1.6595604</v>
+        <v>1.7571816</v>
       </c>
       <c r="N19">
-        <v>-1.5455604</v>
+        <v>-1.6431816</v>
       </c>
       <c r="O19">
-        <v>-0.3709344960000001</v>
+        <v>-0.394363584</v>
       </c>
       <c r="P19">
-        <v>-1.174625904</v>
+        <v>-1.248818016</v>
       </c>
       <c r="Q19">
-        <v>-1.288625904</v>
+        <v>-1.362818016000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1059751902792389</v>
+        <v>0.1067090340631321</v>
       </c>
       <c r="T19">
-        <v>1.014640157086642</v>
+        <v>1.027013817538919</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.01648629359919651</v>
+        <v>0.01557038839924115</v>
       </c>
       <c r="W19">
-        <v>0.2319125319693095</v>
+        <v>0.2321285024154589</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.06869288999665213</v>
+        <v>0.06487661833017144</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3380,22 +3380,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1292845383665509</v>
+        <v>0.1311845383665509</v>
       </c>
       <c r="C20">
-        <v>17.95355606393419</v>
+        <v>17.02362475641386</v>
       </c>
       <c r="D20">
-        <v>23.1855560639342</v>
+        <v>22.66962475641386</v>
       </c>
       <c r="E20">
-        <v>1.652</v>
+        <v>2.066000000000001</v>
       </c>
       <c r="F20">
-        <v>7.452000000000001</v>
+        <v>7.866000000000001</v>
       </c>
       <c r="G20">
         <v>2.22</v>
@@ -3416,37 +3416,37 @@
         <v>0.114</v>
       </c>
       <c r="M20">
-        <v>1.7571816</v>
+        <v>1.8548028</v>
       </c>
       <c r="N20">
-        <v>-1.6431816</v>
+        <v>-1.7408028</v>
       </c>
       <c r="O20">
-        <v>-0.394363584</v>
+        <v>-0.417792672</v>
       </c>
       <c r="P20">
-        <v>-1.248818016</v>
+        <v>-1.323010128</v>
       </c>
       <c r="Q20">
-        <v>-1.362818016</v>
+        <v>-1.437010128</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1067090340631321</v>
+        <v>0.1074609974466275</v>
       </c>
       <c r="T20">
-        <v>1.027013817538919</v>
+        <v>1.039693000471498</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.01557038839924115</v>
+        <v>0.0147508942729653</v>
       </c>
       <c r="W20">
-        <v>0.2321285024154589</v>
+        <v>0.2323217391304348</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.06487661833017155</v>
+        <v>0.06146205947068883</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3462,22 +3462,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1311845383665509</v>
+        <v>0.1330845383665509</v>
       </c>
       <c r="C21">
-        <v>17.02362475641386</v>
+        <v>16.11615491807543</v>
       </c>
       <c r="D21">
-        <v>22.66962475641386</v>
+        <v>22.17615491807543</v>
       </c>
       <c r="E21">
-        <v>2.066000000000001</v>
+        <v>2.48</v>
       </c>
       <c r="F21">
-        <v>7.866000000000001</v>
+        <v>8.280000000000001</v>
       </c>
       <c r="G21">
         <v>2.22</v>
@@ -3498,37 +3498,37 @@
         <v>0.114</v>
       </c>
       <c r="M21">
-        <v>1.8548028</v>
+        <v>1.952424</v>
       </c>
       <c r="N21">
-        <v>-1.7408028</v>
+        <v>-1.838424</v>
       </c>
       <c r="O21">
-        <v>-0.417792672</v>
+        <v>-0.4412217600000001</v>
       </c>
       <c r="P21">
-        <v>-1.323010128</v>
+        <v>-1.39720224</v>
       </c>
       <c r="Q21">
-        <v>-1.437010128</v>
+        <v>-1.51120224</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1074609974466275</v>
+        <v>0.1082317599147104</v>
       </c>
       <c r="T21">
-        <v>1.039693000471498</v>
+        <v>1.052689162977392</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.0147508942729653</v>
+        <v>0.01401334955931703</v>
       </c>
       <c r="W21">
-        <v>0.2323217391304348</v>
+        <v>0.2324956521739131</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.06146205947068883</v>
+        <v>0.05838895649715437</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3544,22 +3544,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1330845383665509</v>
+        <v>0.1349845383665509</v>
       </c>
       <c r="C22">
-        <v>16.11615491807543</v>
+        <v>15.22971098198453</v>
       </c>
       <c r="D22">
-        <v>22.17615491807543</v>
+        <v>21.70371098198453</v>
       </c>
       <c r="E22">
-        <v>2.48</v>
+        <v>2.894000000000002</v>
       </c>
       <c r="F22">
-        <v>8.280000000000001</v>
+        <v>8.694000000000003</v>
       </c>
       <c r="G22">
         <v>2.22</v>
@@ -3580,37 +3580,37 @@
         <v>0.114</v>
       </c>
       <c r="M22">
-        <v>1.952424</v>
+        <v>2.050045200000001</v>
       </c>
       <c r="N22">
-        <v>-1.838424</v>
+        <v>-1.936045200000001</v>
       </c>
       <c r="O22">
-        <v>-0.4412217600000001</v>
+        <v>-0.4646508480000002</v>
       </c>
       <c r="P22">
-        <v>-1.39720224</v>
+        <v>-1.471394352000001</v>
       </c>
       <c r="Q22">
-        <v>-1.51120224</v>
+        <v>-1.585394352000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1082317599147104</v>
+        <v>0.1090220353566687</v>
       </c>
       <c r="T22">
-        <v>1.052689162977392</v>
+        <v>1.066014342255586</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.01401334955931703</v>
+        <v>0.01334604719934955</v>
       </c>
       <c r="W22">
-        <v>0.2324956521739131</v>
+        <v>0.2326530020703934</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.05838895649715437</v>
+        <v>0.05560852999728982</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3626,22 +3626,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1349845383665509</v>
+        <v>0.1368845383665509</v>
       </c>
       <c r="C23">
-        <v>15.22971098198453</v>
+        <v>14.36297716343214</v>
       </c>
       <c r="D23">
-        <v>21.70371098198453</v>
+        <v>21.25097716343214</v>
       </c>
       <c r="E23">
-        <v>2.894</v>
+        <v>3.308</v>
       </c>
       <c r="F23">
-        <v>8.694000000000001</v>
+        <v>9.108000000000001</v>
       </c>
       <c r="G23">
         <v>2.22</v>
@@ -3662,37 +3662,37 @@
         <v>0.114</v>
       </c>
       <c r="M23">
-        <v>2.0500452</v>
+        <v>2.1476664</v>
       </c>
       <c r="N23">
-        <v>-1.9360452</v>
+        <v>-2.0336664</v>
       </c>
       <c r="O23">
-        <v>-0.4646508480000001</v>
+        <v>-0.4880799360000001</v>
       </c>
       <c r="P23">
-        <v>-1.471394352</v>
+        <v>-1.545586464</v>
       </c>
       <c r="Q23">
-        <v>-1.585394352</v>
+        <v>-1.659586464</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1090220353566687</v>
+        <v>0.1098325742714978</v>
       </c>
       <c r="T23">
-        <v>1.066014342255586</v>
+        <v>1.079681192797325</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.01334604719934955</v>
+        <v>0.01273940869028821</v>
       </c>
       <c r="W23">
-        <v>0.2326530020703934</v>
+        <v>0.23279604743083</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.05560852999728982</v>
+        <v>0.0530808695428675</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3708,22 +3708,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1368845383665509</v>
+        <v>0.1387845383665509</v>
       </c>
       <c r="C24">
-        <v>14.36297716343214</v>
+        <v>13.51474522208127</v>
       </c>
       <c r="D24">
-        <v>21.25097716343214</v>
+        <v>20.81674522208128</v>
       </c>
       <c r="E24">
-        <v>3.308</v>
+        <v>3.722000000000001</v>
       </c>
       <c r="F24">
-        <v>9.108000000000001</v>
+        <v>9.522000000000002</v>
       </c>
       <c r="G24">
         <v>2.22</v>
@@ -3744,37 +3744,37 @@
         <v>0.114</v>
       </c>
       <c r="M24">
-        <v>2.1476664</v>
+        <v>2.245287600000001</v>
       </c>
       <c r="N24">
-        <v>-2.0336664</v>
+        <v>-2.131287600000001</v>
       </c>
       <c r="O24">
-        <v>-0.4880799360000001</v>
+        <v>-0.5115090240000002</v>
       </c>
       <c r="P24">
-        <v>-1.545586464</v>
+        <v>-1.619778576000001</v>
       </c>
       <c r="Q24">
-        <v>-1.659586464</v>
+        <v>-1.733778576000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1098325742714978</v>
+        <v>0.1106641661451536</v>
       </c>
       <c r="T24">
-        <v>1.079681192797325</v>
+        <v>1.093703026470017</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.01273940869028821</v>
+        <v>0.01218552135592785</v>
       </c>
       <c r="W24">
-        <v>0.23279604743083</v>
+        <v>0.2329266540642722</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.0530808695428675</v>
+        <v>0.05077300564969933</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3790,22 +3790,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1387845383665509</v>
+        <v>0.1406845383665509</v>
       </c>
       <c r="C25">
-        <v>13.51474522208127</v>
+        <v>12.68390369444311</v>
       </c>
       <c r="D25">
-        <v>20.81674522208128</v>
+        <v>20.39990369444311</v>
       </c>
       <c r="E25">
-        <v>3.722000000000001</v>
+        <v>4.136000000000001</v>
       </c>
       <c r="F25">
-        <v>9.522000000000002</v>
+        <v>9.936000000000002</v>
       </c>
       <c r="G25">
         <v>2.22</v>
@@ -3826,37 +3826,37 @@
         <v>0.114</v>
       </c>
       <c r="M25">
-        <v>2.245287600000001</v>
+        <v>2.3429088</v>
       </c>
       <c r="N25">
-        <v>-2.131287600000001</v>
+        <v>-2.228908800000001</v>
       </c>
       <c r="O25">
-        <v>-0.5115090240000002</v>
+        <v>-0.5349381120000001</v>
       </c>
       <c r="P25">
-        <v>-1.619778576000001</v>
+        <v>-1.693970688000001</v>
       </c>
       <c r="Q25">
-        <v>-1.733778576000001</v>
+        <v>-1.807970688000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1106641661451536</v>
+        <v>0.1115176420154846</v>
       </c>
       <c r="T25">
-        <v>1.093703026470017</v>
+        <v>1.108093855765675</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.01218552135592785</v>
+        <v>0.01167779129943086</v>
       </c>
       <c r="W25">
-        <v>0.2329266540642722</v>
+        <v>0.2330463768115942</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.05077300564969933</v>
+        <v>0.04865746374762858</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3872,22 +3872,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1406845383665509</v>
+        <v>0.1425845383665509</v>
       </c>
       <c r="C26">
-        <v>12.68390369444312</v>
+        <v>11.86942839463183</v>
       </c>
       <c r="D26">
-        <v>20.39990369444312</v>
+        <v>19.99942839463183</v>
       </c>
       <c r="E26">
-        <v>4.136000000000001</v>
+        <v>4.550000000000001</v>
       </c>
       <c r="F26">
-        <v>9.936000000000002</v>
+        <v>10.35</v>
       </c>
       <c r="G26">
         <v>2.22</v>
@@ -3908,37 +3908,37 @@
         <v>0.114</v>
       </c>
       <c r="M26">
-        <v>2.3429088</v>
+        <v>2.44053</v>
       </c>
       <c r="N26">
-        <v>-2.228908800000001</v>
+        <v>-2.32653</v>
       </c>
       <c r="O26">
-        <v>-0.5349381120000001</v>
+        <v>-0.5583672000000001</v>
       </c>
       <c r="P26">
-        <v>-1.693970688000001</v>
+        <v>-1.7681628</v>
       </c>
       <c r="Q26">
-        <v>-1.807970688000001</v>
+        <v>-1.8821628</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1115176420154846</v>
+        <v>0.1123938772423577</v>
       </c>
       <c r="T26">
-        <v>1.108093855765675</v>
+        <v>1.122868440509218</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.01167779129943086</v>
+        <v>0.01121067964745362</v>
       </c>
       <c r="W26">
-        <v>0.2330463768115942</v>
+        <v>0.2331565217391305</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.04865746374762858</v>
+        <v>0.04671116519772334</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3954,22 +3954,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1425845383665509</v>
+        <v>0.1444845383665509</v>
       </c>
       <c r="C27">
-        <v>11.86942839463183</v>
+        <v>11.07037401246855</v>
       </c>
       <c r="D27">
-        <v>19.99942839463183</v>
+        <v>19.61437401246856</v>
       </c>
       <c r="E27">
-        <v>4.550000000000001</v>
+        <v>4.964</v>
       </c>
       <c r="F27">
-        <v>10.35</v>
+        <v>10.764</v>
       </c>
       <c r="G27">
         <v>2.22</v>
@@ -3990,37 +3990,37 @@
         <v>0.114</v>
       </c>
       <c r="M27">
-        <v>2.44053</v>
+        <v>2.5381512</v>
       </c>
       <c r="N27">
-        <v>-2.32653</v>
+        <v>-2.4241512</v>
       </c>
       <c r="O27">
-        <v>-0.5583672000000001</v>
+        <v>-0.5817962880000001</v>
       </c>
       <c r="P27">
-        <v>-1.7681628</v>
+        <v>-1.842354912</v>
       </c>
       <c r="Q27">
-        <v>-1.8821628</v>
+        <v>-1.956354912</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1123938772423577</v>
+        <v>0.1132937945023896</v>
       </c>
       <c r="T27">
-        <v>1.122868440509218</v>
+        <v>1.138042338353937</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.01121067964745362</v>
+        <v>0.0107794996610131</v>
       </c>
       <c r="W27">
-        <v>0.2331565217391305</v>
+        <v>0.2332581939799331</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.04671116519772334</v>
+        <v>0.04491458192088793</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4036,22 +4036,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1444845383665509</v>
+        <v>0.1463845383665509</v>
       </c>
       <c r="C28">
-        <v>11.07037401246855</v>
+        <v>10.28586666383529</v>
       </c>
       <c r="D28">
-        <v>19.61437401246856</v>
+        <v>19.2438666638353</v>
       </c>
       <c r="E28">
-        <v>4.964</v>
+        <v>5.378000000000002</v>
       </c>
       <c r="F28">
-        <v>10.764</v>
+        <v>11.178</v>
       </c>
       <c r="G28">
         <v>2.22</v>
@@ -4072,37 +4072,37 @@
         <v>0.114</v>
       </c>
       <c r="M28">
-        <v>2.5381512</v>
+        <v>2.635772400000001</v>
       </c>
       <c r="N28">
-        <v>-2.4241512</v>
+        <v>-2.521772400000001</v>
       </c>
       <c r="O28">
-        <v>-0.5817962880000001</v>
+        <v>-0.6052253760000003</v>
       </c>
       <c r="P28">
-        <v>-1.842354912</v>
+        <v>-1.916547024000001</v>
       </c>
       <c r="Q28">
-        <v>-1.956354912</v>
+        <v>-2.030547024000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1132937945023896</v>
+        <v>0.1142183670298196</v>
       </c>
       <c r="T28">
-        <v>1.138042338353937</v>
+        <v>1.153631959427278</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.0107794996610131</v>
+        <v>0.01038025893282743</v>
       </c>
       <c r="W28">
-        <v>0.2332581939799331</v>
+        <v>0.2333523349436393</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.04491458192088793</v>
+        <v>0.04325107888678092</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4118,22 +4118,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1463845383665509</v>
+        <v>0.1482845383665509</v>
       </c>
       <c r="C29">
-        <v>10.28586666383529</v>
+        <v>9.515097269699829</v>
       </c>
       <c r="D29">
-        <v>19.2438666638353</v>
+        <v>18.88709726969983</v>
       </c>
       <c r="E29">
-        <v>5.378000000000002</v>
+        <v>5.792000000000002</v>
       </c>
       <c r="F29">
-        <v>11.178</v>
+        <v>11.592</v>
       </c>
       <c r="G29">
         <v>2.22</v>
@@ -4154,37 +4154,37 @@
         <v>0.114</v>
       </c>
       <c r="M29">
-        <v>2.635772400000001</v>
+        <v>2.733393600000001</v>
       </c>
       <c r="N29">
-        <v>-2.521772400000001</v>
+        <v>-2.619393600000001</v>
       </c>
       <c r="O29">
-        <v>-0.6052253760000003</v>
+        <v>-0.6286544640000001</v>
       </c>
       <c r="P29">
-        <v>-1.916547024000001</v>
+        <v>-1.990739136000001</v>
       </c>
       <c r="Q29">
-        <v>-2.030547024000001</v>
+        <v>-2.104739136000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1142183670298196</v>
+        <v>0.115168622127456</v>
       </c>
       <c r="T29">
-        <v>1.153631959427278</v>
+        <v>1.169654625530435</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.01038025893282743</v>
+        <v>0.01000953539951216</v>
       </c>
       <c r="W29">
-        <v>0.2333523349436393</v>
+        <v>0.233439751552795</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.04325107888678092</v>
+        <v>0.04170639749796734</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4200,22 +4200,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1482845383665509</v>
+        <v>0.1501845383665509</v>
       </c>
       <c r="C30">
-        <v>9.515097269699829</v>
+        <v>8.757315658227672</v>
       </c>
       <c r="D30">
-        <v>18.88709726969983</v>
+        <v>18.54331565822768</v>
       </c>
       <c r="E30">
-        <v>5.792000000000002</v>
+        <v>6.206000000000003</v>
       </c>
       <c r="F30">
-        <v>11.592</v>
+        <v>12.006</v>
       </c>
       <c r="G30">
         <v>2.22</v>
@@ -4236,37 +4236,37 @@
         <v>0.114</v>
       </c>
       <c r="M30">
-        <v>2.733393600000001</v>
+        <v>2.831014800000001</v>
       </c>
       <c r="N30">
-        <v>-2.619393600000001</v>
+        <v>-2.717014800000001</v>
       </c>
       <c r="O30">
-        <v>-0.6286544640000001</v>
+        <v>-0.6520835520000002</v>
       </c>
       <c r="P30">
-        <v>-1.990739136000001</v>
+        <v>-2.064931248000001</v>
       </c>
       <c r="Q30">
-        <v>-2.104739136000001</v>
+        <v>-2.178931248000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.115168622127456</v>
+        <v>0.1161456449743216</v>
       </c>
       <c r="T30">
-        <v>1.169654625530435</v>
+        <v>1.186128634340723</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.01000953539951216</v>
+        <v>0.009664379006425536</v>
       </c>
       <c r="W30">
-        <v>0.233439751552795</v>
+        <v>0.2335211394302849</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.04170639749796734</v>
+        <v>0.04026824586010636</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4282,22 +4282,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1501845383665509</v>
+        <v>0.1520845383665509</v>
       </c>
       <c r="C31">
-        <v>8.757315658227682</v>
+        <v>8.01182529949719</v>
       </c>
       <c r="D31">
-        <v>18.54331565822768</v>
+        <v>18.21182529949719</v>
       </c>
       <c r="E31">
-        <v>6.206</v>
+        <v>6.620000000000001</v>
       </c>
       <c r="F31">
-        <v>12.006</v>
+        <v>12.42</v>
       </c>
       <c r="G31">
         <v>2.22</v>
@@ -4318,37 +4318,37 @@
         <v>0.114</v>
       </c>
       <c r="M31">
-        <v>2.8310148</v>
+        <v>2.928636</v>
       </c>
       <c r="N31">
-        <v>-2.7170148</v>
+        <v>-2.814636000000001</v>
       </c>
       <c r="O31">
-        <v>-0.652083552</v>
+        <v>-0.6755126400000001</v>
       </c>
       <c r="P31">
-        <v>-2.064931248</v>
+        <v>-2.139123360000001</v>
       </c>
       <c r="Q31">
-        <v>-2.178931248</v>
+        <v>-2.25312336</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1161456449743216</v>
+        <v>0.117150582759669</v>
       </c>
       <c r="T31">
-        <v>1.186128634340723</v>
+        <v>1.203073329117019</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.00966437900642554</v>
+        <v>0.009342233039544689</v>
       </c>
       <c r="W31">
-        <v>0.2335211394302849</v>
+        <v>0.2335971014492754</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.04026824586010636</v>
+        <v>0.0389259709981028</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4364,22 +4364,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1520845383665509</v>
+        <v>0.1539845383665509</v>
       </c>
       <c r="C32">
-        <v>8.01182529949719</v>
+        <v>7.277978595046646</v>
       </c>
       <c r="D32">
-        <v>18.21182529949719</v>
+        <v>17.89197859504665</v>
       </c>
       <c r="E32">
-        <v>6.620000000000001</v>
+        <v>7.034000000000001</v>
       </c>
       <c r="F32">
-        <v>12.42</v>
+        <v>12.834</v>
       </c>
       <c r="G32">
         <v>2.22</v>
@@ -4400,37 +4400,37 @@
         <v>0.114</v>
       </c>
       <c r="M32">
-        <v>2.928636</v>
+        <v>3.0262572</v>
       </c>
       <c r="N32">
-        <v>-2.814636000000001</v>
+        <v>-2.9122572</v>
       </c>
       <c r="O32">
-        <v>-0.6755126400000001</v>
+        <v>-0.6989417280000001</v>
       </c>
       <c r="P32">
-        <v>-2.139123360000001</v>
+        <v>-2.213315472000001</v>
       </c>
       <c r="Q32">
-        <v>-2.25312336</v>
+        <v>-2.327315472</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.117150582759669</v>
+        <v>0.1181846491764758</v>
       </c>
       <c r="T32">
-        <v>1.203073329117019</v>
+        <v>1.220509174466541</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.009342233039544689</v>
+        <v>0.009040870683430345</v>
       </c>
       <c r="W32">
-        <v>0.2335971014492754</v>
+        <v>0.2336681626928472</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.0389259709981028</v>
+        <v>0.03767029451429305</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4446,22 +4446,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1539845383665509</v>
+        <v>0.1558845383665509</v>
       </c>
       <c r="C33">
-        <v>7.277978595046646</v>
+        <v>6.555172655220693</v>
       </c>
       <c r="D33">
-        <v>17.89197859504665</v>
+        <v>17.5831726552207</v>
       </c>
       <c r="E33">
-        <v>7.034000000000001</v>
+        <v>7.448000000000002</v>
       </c>
       <c r="F33">
-        <v>12.834</v>
+        <v>13.248</v>
       </c>
       <c r="G33">
         <v>2.22</v>
@@ -4482,37 +4482,37 @@
         <v>0.114</v>
       </c>
       <c r="M33">
-        <v>3.0262572</v>
+        <v>3.123878400000001</v>
       </c>
       <c r="N33">
-        <v>-2.9122572</v>
+        <v>-3.009878400000001</v>
       </c>
       <c r="O33">
-        <v>-0.6989417280000001</v>
+        <v>-0.7223708160000002</v>
       </c>
       <c r="P33">
-        <v>-2.213315472000001</v>
+        <v>-2.287507584000001</v>
       </c>
       <c r="Q33">
-        <v>-2.327315472</v>
+        <v>-2.401507584</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1181846491764758</v>
+        <v>0.119249129311424</v>
       </c>
       <c r="T33">
-        <v>1.220509174466541</v>
+        <v>1.238457838796931</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.009040870683430345</v>
+        <v>0.008758343474573145</v>
       </c>
       <c r="W33">
-        <v>0.2336681626928472</v>
+        <v>0.2337347826086957</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.03767029451429305</v>
+        <v>0.03649309781072141</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4528,22 +4528,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1558845383665509</v>
+        <v>0.1577845383665509</v>
       </c>
       <c r="C34">
-        <v>6.555172655220693</v>
+        <v>5.842845506381916</v>
       </c>
       <c r="D34">
-        <v>17.5831726552207</v>
+        <v>17.28484550638192</v>
       </c>
       <c r="E34">
-        <v>7.448000000000002</v>
+        <v>7.862000000000002</v>
       </c>
       <c r="F34">
-        <v>13.248</v>
+        <v>13.662</v>
       </c>
       <c r="G34">
         <v>2.22</v>
@@ -4564,37 +4564,37 @@
         <v>0.114</v>
       </c>
       <c r="M34">
-        <v>3.123878400000001</v>
+        <v>3.221499600000001</v>
       </c>
       <c r="N34">
-        <v>-3.009878400000001</v>
+        <v>-3.107499600000001</v>
       </c>
       <c r="O34">
-        <v>-0.7223708160000002</v>
+        <v>-0.7457999040000002</v>
       </c>
       <c r="P34">
-        <v>-2.287507584000001</v>
+        <v>-2.361699696000001</v>
       </c>
       <c r="Q34">
-        <v>-2.401507584</v>
+        <v>-2.475699696000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.119249129311424</v>
+        <v>0.1203453849727885</v>
       </c>
       <c r="T34">
-        <v>1.238457838796931</v>
+        <v>1.256942284152109</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.008758343474573145</v>
+        <v>0.008492939126858806</v>
       </c>
       <c r="W34">
-        <v>0.2337347826086957</v>
+        <v>0.2337973649538867</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4602,7 +4602,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.03649309781072141</v>
+        <v>0.03538724636191171</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4610,22 +4610,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1577845383665509</v>
+        <v>0.1596845383665509</v>
       </c>
       <c r="C35">
-        <v>5.842845506381916</v>
+        <v>5.1404726777858</v>
       </c>
       <c r="D35">
-        <v>17.28484550638192</v>
+        <v>16.9964726777858</v>
       </c>
       <c r="E35">
-        <v>7.862000000000002</v>
+        <v>8.276000000000002</v>
       </c>
       <c r="F35">
-        <v>13.662</v>
+        <v>14.076</v>
       </c>
       <c r="G35">
         <v>2.22</v>
@@ -4646,37 +4646,37 @@
         <v>0.114</v>
       </c>
       <c r="M35">
-        <v>3.221499600000001</v>
+        <v>3.319120800000001</v>
       </c>
       <c r="N35">
-        <v>-3.107499600000001</v>
+        <v>-3.205120800000001</v>
       </c>
       <c r="O35">
-        <v>-0.7457999040000002</v>
+        <v>-0.7692289920000002</v>
       </c>
       <c r="P35">
-        <v>-2.361699696000001</v>
+        <v>-2.435891808000001</v>
       </c>
       <c r="Q35">
-        <v>-2.475699696000001</v>
+        <v>-2.549891808000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1203453849727885</v>
+        <v>0.1214748605026792</v>
       </c>
       <c r="T35">
-        <v>1.256942284152109</v>
+        <v>1.27598686421502</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.008492939126858806</v>
+        <v>0.008243146799598254</v>
       </c>
       <c r="W35">
-        <v>0.2337973649538867</v>
+        <v>0.2338562659846548</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.03538724636191171</v>
+        <v>0.03434644499832606</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4692,22 +4692,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1596845383665509</v>
+        <v>0.1615845383665509</v>
       </c>
       <c r="C36">
-        <v>5.1404726777858</v>
+        <v>4.447564124507652</v>
       </c>
       <c r="D36">
-        <v>16.9964726777858</v>
+        <v>16.71756412450766</v>
       </c>
       <c r="E36">
-        <v>8.276000000000002</v>
+        <v>8.690000000000003</v>
       </c>
       <c r="F36">
-        <v>14.076</v>
+        <v>14.49</v>
       </c>
       <c r="G36">
         <v>2.22</v>
@@ -4728,37 +4728,37 @@
         <v>0.114</v>
       </c>
       <c r="M36">
-        <v>3.319120800000001</v>
+        <v>3.416742000000001</v>
       </c>
       <c r="N36">
-        <v>-3.205120800000001</v>
+        <v>-3.302742000000001</v>
       </c>
       <c r="O36">
-        <v>-0.7692289920000002</v>
+        <v>-0.7926580800000003</v>
       </c>
       <c r="P36">
-        <v>-2.435891808000001</v>
+        <v>-2.510083920000001</v>
       </c>
       <c r="Q36">
-        <v>-2.549891808000001</v>
+        <v>-2.624083920000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1214748605026792</v>
+        <v>0.1226390891257974</v>
       </c>
       <c r="T36">
-        <v>1.27598686421502</v>
+        <v>1.29561743135679</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.008243146799598254</v>
+        <v>0.008007628319609732</v>
       </c>
       <c r="W36">
-        <v>0.2338562659846548</v>
+        <v>0.233911801242236</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.03434644499832606</v>
+        <v>0.03336511799837383</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4774,22 +4774,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1615845383665509</v>
+        <v>0.1634845383665509</v>
       </c>
       <c r="C37">
-        <v>4.447564124507652</v>
+        <v>3.763661448443003</v>
       </c>
       <c r="D37">
-        <v>16.71756412450766</v>
+        <v>16.44766144844301</v>
       </c>
       <c r="E37">
-        <v>8.690000000000003</v>
+        <v>9.104000000000003</v>
       </c>
       <c r="F37">
-        <v>14.49</v>
+        <v>14.904</v>
       </c>
       <c r="G37">
         <v>2.22</v>
@@ -4810,37 +4810,37 @@
         <v>0.114</v>
       </c>
       <c r="M37">
-        <v>3.416742000000001</v>
+        <v>3.514363200000001</v>
       </c>
       <c r="N37">
-        <v>-3.302742000000001</v>
+        <v>-3.400363200000001</v>
       </c>
       <c r="O37">
-        <v>-0.7926580800000003</v>
+        <v>-0.8160871680000003</v>
       </c>
       <c r="P37">
-        <v>-2.510083920000001</v>
+        <v>-2.584276032000001</v>
       </c>
       <c r="Q37">
-        <v>-2.624083920000001</v>
+        <v>-2.698276032000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1226390891257974</v>
+        <v>0.123839699893388</v>
       </c>
       <c r="T37">
-        <v>1.29561743135679</v>
+        <v>1.31586145372174</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.008007628319609732</v>
+        <v>0.007785194199620573</v>
       </c>
       <c r="W37">
-        <v>0.233911801242236</v>
+        <v>0.2339642512077295</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.03336511799837383</v>
+        <v>0.03243830916508572</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4856,22 +4856,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1634845383665509</v>
+        <v>0.1653845383665509</v>
       </c>
       <c r="C38">
-        <v>3.763661448443004</v>
+        <v>3.088335384230152</v>
       </c>
       <c r="D38">
-        <v>16.44766144844301</v>
+        <v>16.18633538423015</v>
       </c>
       <c r="E38">
-        <v>9.104000000000001</v>
+        <v>9.518000000000001</v>
       </c>
       <c r="F38">
-        <v>14.904</v>
+        <v>15.318</v>
       </c>
       <c r="G38">
         <v>2.22</v>
@@ -4892,37 +4892,37 @@
         <v>0.114</v>
       </c>
       <c r="M38">
-        <v>3.5143632</v>
+        <v>3.6119844</v>
       </c>
       <c r="N38">
-        <v>-3.400363200000001</v>
+        <v>-3.4979844</v>
       </c>
       <c r="O38">
-        <v>-0.8160871680000001</v>
+        <v>-0.8395162560000001</v>
       </c>
       <c r="P38">
-        <v>-2.584276032</v>
+        <v>-2.658468144</v>
       </c>
       <c r="Q38">
-        <v>-2.698276032</v>
+        <v>-2.772468144</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.123839699893388</v>
+        <v>0.1250784252885211</v>
       </c>
       <c r="T38">
-        <v>1.315861453721739</v>
+        <v>1.336748143463354</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.007785194199620573</v>
+        <v>0.007574783545576775</v>
       </c>
       <c r="W38">
-        <v>0.2339642512077295</v>
+        <v>0.234013866039953</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.03243830916508572</v>
+        <v>0.03156159810656989</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4938,22 +4938,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1653845383665509</v>
+        <v>0.1672845383665509</v>
       </c>
       <c r="C39">
-        <v>3.088335384230152</v>
+        <v>2.42118352109145</v>
       </c>
       <c r="D39">
-        <v>16.18633538423015</v>
+        <v>15.93318352109145</v>
       </c>
       <c r="E39">
-        <v>9.518000000000001</v>
+        <v>9.932000000000002</v>
       </c>
       <c r="F39">
-        <v>15.318</v>
+        <v>15.732</v>
       </c>
       <c r="G39">
         <v>2.22</v>
@@ -4974,37 +4974,37 @@
         <v>0.114</v>
       </c>
       <c r="M39">
-        <v>3.6119844</v>
+        <v>3.709605600000001</v>
       </c>
       <c r="N39">
-        <v>-3.4979844</v>
+        <v>-3.595605600000001</v>
       </c>
       <c r="O39">
-        <v>-0.8395162560000001</v>
+        <v>-0.8629453440000001</v>
       </c>
       <c r="P39">
-        <v>-2.658468144</v>
+        <v>-2.732660256000001</v>
       </c>
       <c r="Q39">
-        <v>-2.772468144</v>
+        <v>-2.846660256000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1250784252885211</v>
+        <v>0.1263571095673682</v>
       </c>
       <c r="T39">
-        <v>1.336748143463354</v>
+        <v>1.358308597390183</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.007574783545576775</v>
+        <v>0.007375447136482648</v>
       </c>
       <c r="W39">
-        <v>0.234013866039953</v>
+        <v>0.2340608695652174</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.03156159810656989</v>
+        <v>0.03073102973534436</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5020,22 +5020,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1672845383665509</v>
+        <v>0.1691845383665509</v>
       </c>
       <c r="C40">
-        <v>2.42118352109145</v>
+        <v>1.761828235163012</v>
       </c>
       <c r="D40">
-        <v>15.93318352109145</v>
+        <v>15.68782823516302</v>
       </c>
       <c r="E40">
-        <v>9.932000000000002</v>
+        <v>10.346</v>
       </c>
       <c r="F40">
-        <v>15.732</v>
+        <v>16.146</v>
       </c>
       <c r="G40">
         <v>2.22</v>
@@ -5056,37 +5056,37 @@
         <v>0.114</v>
       </c>
       <c r="M40">
-        <v>3.709605600000001</v>
+        <v>3.807226800000001</v>
       </c>
       <c r="N40">
-        <v>-3.595605600000001</v>
+        <v>-3.693226800000001</v>
       </c>
       <c r="O40">
-        <v>-0.8629453440000001</v>
+        <v>-0.8863744320000003</v>
       </c>
       <c r="P40">
-        <v>-2.732660256000001</v>
+        <v>-2.806852368000001</v>
       </c>
       <c r="Q40">
-        <v>-2.846660256000001</v>
+        <v>-2.920852368000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1263571095673682</v>
+        <v>0.1276777179209316</v>
       </c>
       <c r="T40">
-        <v>1.358308597390183</v>
+        <v>1.380575951445759</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.007375447136482648</v>
+        <v>0.007186333107342065</v>
       </c>
       <c r="W40">
-        <v>0.2340608695652174</v>
+        <v>0.2341054626532887</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.03073102973534436</v>
+        <v>0.02994305461392521</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5102,22 +5102,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1691845383665509</v>
+        <v>0.1710845383665509</v>
       </c>
       <c r="C41">
-        <v>1.761828235163012</v>
+        <v>1.109914809967623</v>
       </c>
       <c r="D41">
-        <v>15.68782823516302</v>
+        <v>15.44991480996763</v>
       </c>
       <c r="E41">
-        <v>10.346</v>
+        <v>10.76</v>
       </c>
       <c r="F41">
-        <v>16.146</v>
+        <v>16.56</v>
       </c>
       <c r="G41">
         <v>2.22</v>
@@ -5138,37 +5138,37 @@
         <v>0.114</v>
       </c>
       <c r="M41">
-        <v>3.807226800000001</v>
+        <v>3.904848000000001</v>
       </c>
       <c r="N41">
-        <v>-3.693226800000001</v>
+        <v>-3.790848000000001</v>
       </c>
       <c r="O41">
-        <v>-0.8863744320000003</v>
+        <v>-0.9098035200000002</v>
       </c>
       <c r="P41">
-        <v>-2.806852368000001</v>
+        <v>-2.881044480000001</v>
       </c>
       <c r="Q41">
-        <v>-2.920852368000001</v>
+        <v>-2.995044480000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1276777179209316</v>
+        <v>0.1290423465529472</v>
       </c>
       <c r="T41">
-        <v>1.380575951445759</v>
+        <v>1.403585550636522</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.007186333107342065</v>
+        <v>0.007006674779658515</v>
       </c>
       <c r="W41">
-        <v>0.2341054626532887</v>
+        <v>0.2341478260869565</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.02994305461392521</v>
+        <v>0.02919447824857713</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5184,22 +5184,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1710845383665509</v>
+        <v>0.1729845383665509</v>
       </c>
       <c r="C42">
-        <v>1.109914809967623</v>
+        <v>0.4651097253563385</v>
       </c>
       <c r="D42">
-        <v>15.44991480996763</v>
+        <v>15.21910972535634</v>
       </c>
       <c r="E42">
-        <v>10.76</v>
+        <v>11.174</v>
       </c>
       <c r="F42">
-        <v>16.56</v>
+        <v>16.974</v>
       </c>
       <c r="G42">
         <v>2.22</v>
@@ -5220,37 +5220,37 @@
         <v>0.114</v>
       </c>
       <c r="M42">
-        <v>3.904848000000001</v>
+        <v>4.002469200000001</v>
       </c>
       <c r="N42">
-        <v>-3.790848000000001</v>
+        <v>-3.888469200000001</v>
       </c>
       <c r="O42">
-        <v>-0.9098035200000002</v>
+        <v>-0.9332326080000003</v>
       </c>
       <c r="P42">
-        <v>-2.881044480000001</v>
+        <v>-2.955236592000001</v>
       </c>
       <c r="Q42">
-        <v>-2.995044480000001</v>
+        <v>-3.069236592000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1290423465529472</v>
+        <v>0.1304532337826581</v>
       </c>
       <c r="T42">
-        <v>1.403585550636522</v>
+        <v>1.427375136240531</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.007006674779658515</v>
+        <v>0.006835780272837576</v>
       </c>
       <c r="W42">
-        <v>0.2341478260869565</v>
+        <v>0.2341881230116649</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.02919447824857713</v>
+        <v>0.02848241780348992</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5266,22 +5266,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1729845383665509</v>
+        <v>0.1748845383665509</v>
       </c>
       <c r="C43">
-        <v>0.4651097253563385</v>
+        <v>-0.1729009024391175</v>
       </c>
       <c r="D43">
-        <v>15.21910972535634</v>
+        <v>14.99509909756089</v>
       </c>
       <c r="E43">
-        <v>11.174</v>
+        <v>11.588</v>
       </c>
       <c r="F43">
-        <v>16.974</v>
+        <v>17.38800000000001</v>
       </c>
       <c r="G43">
         <v>2.22</v>
@@ -5302,37 +5302,37 @@
         <v>0.114</v>
       </c>
       <c r="M43">
-        <v>4.002469200000001</v>
+        <v>4.100090400000002</v>
       </c>
       <c r="N43">
-        <v>-3.888469200000001</v>
+        <v>-3.986090400000002</v>
       </c>
       <c r="O43">
-        <v>-0.9332326080000003</v>
+        <v>-0.9566616960000004</v>
       </c>
       <c r="P43">
-        <v>-2.955236592000001</v>
+        <v>-3.029428704000002</v>
       </c>
       <c r="Q43">
-        <v>-3.069236592000001</v>
+        <v>-3.143428704000002</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1304532337826581</v>
+        <v>0.1319127722961522</v>
       </c>
       <c r="T43">
-        <v>1.427375136240531</v>
+        <v>1.451985052382609</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.006835780272837576</v>
+        <v>0.006673023599674775</v>
       </c>
       <c r="W43">
-        <v>0.2341881230116649</v>
+        <v>0.2342265010351967</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.02848241780348992</v>
+        <v>0.02780426499864486</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5348,22 +5348,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1748845383665509</v>
+        <v>0.1767845383665509</v>
       </c>
       <c r="C44">
-        <v>-0.1729009024391139</v>
+        <v>-0.8044127449867915</v>
       </c>
       <c r="D44">
-        <v>14.99509909756089</v>
+        <v>14.77758725501321</v>
       </c>
       <c r="E44">
-        <v>11.588</v>
+        <v>12.002</v>
       </c>
       <c r="F44">
-        <v>17.388</v>
+        <v>17.802</v>
       </c>
       <c r="G44">
         <v>2.22</v>
@@ -5384,37 +5384,37 @@
         <v>0.114</v>
       </c>
       <c r="M44">
-        <v>4.100090400000001</v>
+        <v>4.197711600000001</v>
       </c>
       <c r="N44">
-        <v>-3.986090400000001</v>
+        <v>-4.083711600000001</v>
       </c>
       <c r="O44">
-        <v>-0.9566616960000002</v>
+        <v>-0.9800907840000002</v>
       </c>
       <c r="P44">
-        <v>-3.029428704000001</v>
+        <v>-3.103620816000001</v>
       </c>
       <c r="Q44">
-        <v>-3.143428704000001</v>
+        <v>-3.217620816000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1319127722961522</v>
+        <v>0.1334235226873128</v>
       </c>
       <c r="T44">
-        <v>1.451985052382609</v>
+        <v>1.477458474354234</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.006673023599674776</v>
+        <v>0.006517837004333503</v>
       </c>
       <c r="W44">
-        <v>0.2342265010351967</v>
+        <v>0.2342630940343782</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.02780426499864486</v>
+        <v>0.02715765418472293</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5430,22 +5430,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1767845383665509</v>
+        <v>0.1786845383665509</v>
       </c>
       <c r="C45">
-        <v>-0.8044127449867915</v>
+        <v>-1.429704563656291</v>
       </c>
       <c r="D45">
-        <v>14.77758725501321</v>
+        <v>14.56629543634371</v>
       </c>
       <c r="E45">
-        <v>12.002</v>
+        <v>12.416</v>
       </c>
       <c r="F45">
-        <v>17.802</v>
+        <v>18.216</v>
       </c>
       <c r="G45">
         <v>2.22</v>
@@ -5466,37 +5466,37 @@
         <v>0.114</v>
       </c>
       <c r="M45">
-        <v>4.197711600000001</v>
+        <v>4.295332800000001</v>
       </c>
       <c r="N45">
-        <v>-4.083711600000001</v>
+        <v>-4.181332800000001</v>
       </c>
       <c r="O45">
-        <v>-0.9800907840000002</v>
+        <v>-1.003519872</v>
       </c>
       <c r="P45">
-        <v>-3.103620816000001</v>
+        <v>-3.177812928000001</v>
       </c>
       <c r="Q45">
-        <v>-3.217620816000001</v>
+        <v>-3.291812928000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1334235226873128</v>
+        <v>0.1349882284495862</v>
       </c>
       <c r="T45">
-        <v>1.477458474354234</v>
+        <v>1.503841661396274</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.006517837004333503</v>
+        <v>0.006369704345144105</v>
       </c>
       <c r="W45">
-        <v>0.2342630940343782</v>
+        <v>0.2342980237154151</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.02715765418472293</v>
+        <v>0.02654043477143375</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5512,22 +5512,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1786845383665509</v>
+        <v>0.1805845383665509</v>
       </c>
       <c r="C46">
-        <v>-1.429704563656291</v>
+        <v>-2.049039401497904</v>
       </c>
       <c r="D46">
-        <v>14.56629543634371</v>
+        <v>14.3609605985021</v>
       </c>
       <c r="E46">
-        <v>12.416</v>
+        <v>12.83</v>
       </c>
       <c r="F46">
-        <v>18.216</v>
+        <v>18.63</v>
       </c>
       <c r="G46">
         <v>2.22</v>
@@ -5548,37 +5548,37 @@
         <v>0.114</v>
       </c>
       <c r="M46">
-        <v>4.295332800000001</v>
+        <v>4.392954</v>
       </c>
       <c r="N46">
-        <v>-4.181332800000001</v>
+        <v>-4.278954000000001</v>
       </c>
       <c r="O46">
-        <v>-1.003519872</v>
+        <v>-1.02694896</v>
       </c>
       <c r="P46">
-        <v>-3.177812928000001</v>
+        <v>-3.25200504</v>
       </c>
       <c r="Q46">
-        <v>-3.291812928000001</v>
+        <v>-3.36600504</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1349882284495862</v>
+        <v>0.1366098326032151</v>
       </c>
       <c r="T46">
-        <v>1.503841661396274</v>
+        <v>1.531184237058024</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.006369704345144105</v>
+        <v>0.006228155359696458</v>
       </c>
       <c r="W46">
-        <v>0.2342980237154151</v>
+        <v>0.2343314009661836</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.02654043477143375</v>
+        <v>0.02595064733206853</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5594,22 +5594,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1805845383665509</v>
+        <v>0.1824845383665509</v>
       </c>
       <c r="C47">
-        <v>-2.049039401497904</v>
+        <v>-2.662665675714681</v>
       </c>
       <c r="D47">
-        <v>14.3609605985021</v>
+        <v>14.16133432428532</v>
       </c>
       <c r="E47">
-        <v>12.83</v>
+        <v>13.244</v>
       </c>
       <c r="F47">
-        <v>18.63</v>
+        <v>19.044</v>
       </c>
       <c r="G47">
         <v>2.22</v>
@@ -5630,37 +5630,37 @@
         <v>0.114</v>
       </c>
       <c r="M47">
-        <v>4.392954</v>
+        <v>4.490575200000001</v>
       </c>
       <c r="N47">
-        <v>-4.278954000000001</v>
+        <v>-4.376575200000001</v>
       </c>
       <c r="O47">
-        <v>-1.02694896</v>
+        <v>-1.050378048</v>
       </c>
       <c r="P47">
-        <v>-3.25200504</v>
+        <v>-3.326197152000001</v>
       </c>
       <c r="Q47">
-        <v>-3.36600504</v>
+        <v>-3.440197152000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1366098326032151</v>
+        <v>0.1382914961699413</v>
       </c>
       <c r="T47">
-        <v>1.531184237058024</v>
+        <v>1.559539500707247</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.006228155359696458</v>
+        <v>0.006092760677963926</v>
       </c>
       <c r="W47">
-        <v>0.2343314009661836</v>
+        <v>0.2343633270321361</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.02595064733206853</v>
+        <v>0.02538650282484967</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5676,22 +5676,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1824845383665509</v>
+        <v>0.1843845383665509</v>
       </c>
       <c r="C48">
-        <v>-2.662665675714681</v>
+        <v>-3.270818180267359</v>
       </c>
       <c r="D48">
-        <v>14.16133432428532</v>
+        <v>13.96718181973265</v>
       </c>
       <c r="E48">
-        <v>13.244</v>
+        <v>13.658</v>
       </c>
       <c r="F48">
-        <v>19.044</v>
+        <v>19.45800000000001</v>
       </c>
       <c r="G48">
         <v>2.22</v>
@@ -5712,37 +5712,37 @@
         <v>0.114</v>
       </c>
       <c r="M48">
-        <v>4.490575200000001</v>
+        <v>4.588196400000001</v>
       </c>
       <c r="N48">
-        <v>-4.376575200000001</v>
+        <v>-4.474196400000001</v>
       </c>
       <c r="O48">
-        <v>-1.050378048</v>
+        <v>-1.073807136</v>
       </c>
       <c r="P48">
-        <v>-3.326197152000001</v>
+        <v>-3.400389264000001</v>
       </c>
       <c r="Q48">
-        <v>-3.440197152000001</v>
+        <v>-3.514389264000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1382914961699413</v>
+        <v>0.1400366187391855</v>
       </c>
       <c r="T48">
-        <v>1.559539500707247</v>
+        <v>1.588964774305497</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.006092760677963926</v>
+        <v>0.0059631274720498</v>
       </c>
       <c r="W48">
-        <v>0.2343633270321361</v>
+        <v>0.2343938945420907</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.02538650282484967</v>
+        <v>0.02484636446687416</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5758,22 +5758,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1843845383665509</v>
+        <v>0.1862845383665509</v>
       </c>
       <c r="C49">
-        <v>-3.270818180267359</v>
+        <v>-3.873719007120275</v>
       </c>
       <c r="D49">
-        <v>13.96718181973265</v>
+        <v>13.77828099287973</v>
       </c>
       <c r="E49">
-        <v>13.658</v>
+        <v>14.072</v>
       </c>
       <c r="F49">
-        <v>19.45800000000001</v>
+        <v>19.872</v>
       </c>
       <c r="G49">
         <v>2.22</v>
@@ -5794,37 +5794,37 @@
         <v>0.114</v>
       </c>
       <c r="M49">
-        <v>4.588196400000001</v>
+        <v>4.685817600000001</v>
       </c>
       <c r="N49">
-        <v>-4.474196400000001</v>
+        <v>-4.571817600000001</v>
       </c>
       <c r="O49">
-        <v>-1.073807136</v>
+        <v>-1.097236224</v>
       </c>
       <c r="P49">
-        <v>-3.400389264000001</v>
+        <v>-3.474581376000001</v>
       </c>
       <c r="Q49">
-        <v>-3.514389264000001</v>
+        <v>-3.588581376</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1400366187391855</v>
+        <v>0.1418488614072467</v>
       </c>
       <c r="T49">
-        <v>1.588964774305497</v>
+        <v>1.619521789195987</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0059631274720498</v>
+        <v>0.005838895649715429</v>
       </c>
       <c r="W49">
-        <v>0.2343938945420907</v>
+        <v>0.2344231884057971</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.02484636446687416</v>
+        <v>0.02432873187381424</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5840,22 +5840,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1862845383665509</v>
+        <v>0.1881845383665509</v>
       </c>
       <c r="C50">
-        <v>-3.87371900712027</v>
+        <v>-4.471578393727809</v>
       </c>
       <c r="D50">
-        <v>13.77828099287973</v>
+        <v>13.59442160627219</v>
       </c>
       <c r="E50">
-        <v>14.072</v>
+        <v>14.486</v>
       </c>
       <c r="F50">
-        <v>19.872</v>
+        <v>20.286</v>
       </c>
       <c r="G50">
         <v>2.22</v>
@@ -5876,37 +5876,37 @@
         <v>0.114</v>
       </c>
       <c r="M50">
-        <v>4.685817600000001</v>
+        <v>4.783438800000001</v>
       </c>
       <c r="N50">
-        <v>-4.571817600000001</v>
+        <v>-4.669438800000001</v>
       </c>
       <c r="O50">
-        <v>-1.097236224</v>
+        <v>-1.120665312</v>
       </c>
       <c r="P50">
-        <v>-3.474581376000001</v>
+        <v>-3.548773488000001</v>
       </c>
       <c r="Q50">
-        <v>-3.588581376</v>
+        <v>-3.662773488000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1418488614072467</v>
+        <v>0.143732172415232</v>
       </c>
       <c r="T50">
-        <v>1.619521789195987</v>
+        <v>1.651277118395908</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.005838895649715429</v>
+        <v>0.005719734514006951</v>
       </c>
       <c r="W50">
-        <v>0.2344231884057971</v>
+        <v>0.2344512866015972</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.02432873187381424</v>
+        <v>0.02383222714169564</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5922,22 +5922,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1881845383665509</v>
+        <v>0.1900845383665509</v>
       </c>
       <c r="C51">
-        <v>-4.471578393727809</v>
+        <v>-5.064595503560456</v>
       </c>
       <c r="D51">
-        <v>13.59442160627219</v>
+        <v>13.41540449643955</v>
       </c>
       <c r="E51">
-        <v>14.486</v>
+        <v>14.9</v>
       </c>
       <c r="F51">
-        <v>20.286</v>
+        <v>20.7</v>
       </c>
       <c r="G51">
         <v>2.22</v>
@@ -5958,37 +5958,37 @@
         <v>0.114</v>
       </c>
       <c r="M51">
-        <v>4.783438800000001</v>
+        <v>4.881060000000001</v>
       </c>
       <c r="N51">
-        <v>-4.669438800000001</v>
+        <v>-4.767060000000001</v>
       </c>
       <c r="O51">
-        <v>-1.120665312</v>
+        <v>-1.1440944</v>
       </c>
       <c r="P51">
-        <v>-3.548773488000001</v>
+        <v>-3.622965600000001</v>
       </c>
       <c r="Q51">
-        <v>-3.662773488000001</v>
+        <v>-3.7369656</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.143732172415232</v>
+        <v>0.1456908158635366</v>
       </c>
       <c r="T51">
-        <v>1.651277118395908</v>
+        <v>1.684302660763827</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.005719734514006951</v>
+        <v>0.005605339823726812</v>
       </c>
       <c r="W51">
-        <v>0.2344512866015972</v>
+        <v>0.2344782608695652</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.02383222714169564</v>
+        <v>0.02335558259886172</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6004,22 +6004,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1900845383665509</v>
+        <v>0.1919845383665509</v>
       </c>
       <c r="C52">
-        <v>-5.064595503560456</v>
+        <v>-5.652959145762628</v>
       </c>
       <c r="D52">
-        <v>13.41540449643955</v>
+        <v>13.24104085423738</v>
       </c>
       <c r="E52">
-        <v>14.9</v>
+        <v>15.314</v>
       </c>
       <c r="F52">
-        <v>20.7</v>
+        <v>21.114</v>
       </c>
       <c r="G52">
         <v>2.22</v>
@@ -6040,37 +6040,37 @@
         <v>0.114</v>
       </c>
       <c r="M52">
-        <v>4.881060000000001</v>
+        <v>4.978681200000001</v>
       </c>
       <c r="N52">
-        <v>-4.767060000000001</v>
+        <v>-4.864681200000001</v>
       </c>
       <c r="O52">
-        <v>-1.1440944</v>
+        <v>-1.167523488</v>
       </c>
       <c r="P52">
-        <v>-3.622965600000001</v>
+        <v>-3.697157712000001</v>
       </c>
       <c r="Q52">
-        <v>-3.7369656</v>
+        <v>-3.811157712000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1456908158635366</v>
+        <v>0.1477294039423843</v>
       </c>
       <c r="T52">
-        <v>1.684302660763827</v>
+        <v>1.718676184452884</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.005605339823726812</v>
+        <v>0.005495431199732169</v>
       </c>
       <c r="W52">
-        <v>0.2344782608695652</v>
+        <v>0.2345041773231032</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.02335558259886172</v>
+        <v>0.02289762999888401</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6086,22 +6086,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1919845383665509</v>
+        <v>0.1938845383665509</v>
       </c>
       <c r="C53">
-        <v>-5.652959145762628</v>
+        <v>-6.236848439409055</v>
       </c>
       <c r="D53">
-        <v>13.24104085423738</v>
+        <v>13.07115156059095</v>
       </c>
       <c r="E53">
-        <v>15.314</v>
+        <v>15.728</v>
       </c>
       <c r="F53">
-        <v>21.114</v>
+        <v>21.528</v>
       </c>
       <c r="G53">
         <v>2.22</v>
@@ -6122,37 +6122,37 @@
         <v>0.114</v>
       </c>
       <c r="M53">
-        <v>4.978681200000001</v>
+        <v>5.0763024</v>
       </c>
       <c r="N53">
-        <v>-4.864681200000001</v>
+        <v>-4.9623024</v>
       </c>
       <c r="O53">
-        <v>-1.167523488</v>
+        <v>-1.190952576</v>
       </c>
       <c r="P53">
-        <v>-3.697157712000001</v>
+        <v>-3.771349824000001</v>
       </c>
       <c r="Q53">
-        <v>-3.811157712000001</v>
+        <v>-3.885349824</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1477294039423843</v>
+        <v>0.149852933191184</v>
       </c>
       <c r="T53">
-        <v>1.718676184452884</v>
+        <v>1.754481938295653</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.005495431199732169</v>
+        <v>0.005389749830506551</v>
       </c>
       <c r="W53">
-        <v>0.2345041773231032</v>
+        <v>0.2345290969899666</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.02289762999888401</v>
+        <v>0.02245729096044391</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6168,22 +6168,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1938845383665509</v>
+        <v>0.1957845383665509</v>
       </c>
       <c r="C54">
-        <v>-6.236848439409055</v>
+        <v>-6.816433427272457</v>
       </c>
       <c r="D54">
-        <v>13.07115156059095</v>
+        <v>12.90556657272755</v>
       </c>
       <c r="E54">
-        <v>15.728</v>
+        <v>16.142</v>
       </c>
       <c r="F54">
-        <v>21.528</v>
+        <v>21.942</v>
       </c>
       <c r="G54">
         <v>2.22</v>
@@ -6204,37 +6204,37 @@
         <v>0.114</v>
       </c>
       <c r="M54">
-        <v>5.0763024</v>
+        <v>5.173923600000001</v>
       </c>
       <c r="N54">
-        <v>-4.9623024</v>
+        <v>-5.059923600000001</v>
       </c>
       <c r="O54">
-        <v>-1.190952576</v>
+        <v>-1.214381664</v>
       </c>
       <c r="P54">
-        <v>-3.771349824000001</v>
+        <v>-3.845541936000001</v>
       </c>
       <c r="Q54">
-        <v>-3.885349824</v>
+        <v>-3.959541936000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.149852933191184</v>
+        <v>0.1520668253867411</v>
       </c>
       <c r="T54">
-        <v>1.754481938295653</v>
+        <v>1.791811341238114</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.005389749830506551</v>
+        <v>0.005288056437478124</v>
       </c>
       <c r="W54">
-        <v>0.2345290969899666</v>
+        <v>0.2345530762920427</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.02245729096044391</v>
+        <v>0.02203356848949212</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6250,22 +6250,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1957845383665509</v>
+        <v>0.1976845383665509</v>
       </c>
       <c r="C55">
-        <v>-6.816433427272457</v>
+        <v>-7.391875643523633</v>
       </c>
       <c r="D55">
-        <v>12.90556657272755</v>
+        <v>12.74412435647637</v>
       </c>
       <c r="E55">
-        <v>16.142</v>
+        <v>16.556</v>
       </c>
       <c r="F55">
-        <v>21.942</v>
+        <v>22.35600000000001</v>
       </c>
       <c r="G55">
         <v>2.22</v>
@@ -6286,37 +6286,37 @@
         <v>0.114</v>
       </c>
       <c r="M55">
-        <v>5.173923600000001</v>
+        <v>5.271544800000002</v>
       </c>
       <c r="N55">
-        <v>-5.059923600000001</v>
+        <v>-5.157544800000002</v>
       </c>
       <c r="O55">
-        <v>-1.214381664</v>
+        <v>-1.237810752</v>
       </c>
       <c r="P55">
-        <v>-3.845541936000001</v>
+        <v>-3.919734048000001</v>
       </c>
       <c r="Q55">
-        <v>-3.959541936000001</v>
+        <v>-4.033734048000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1520668253867411</v>
+        <v>0.1543769737647137</v>
       </c>
       <c r="T55">
-        <v>1.791811341238114</v>
+        <v>1.830763761699811</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.005288056437478124</v>
+        <v>0.005190129466413714</v>
       </c>
       <c r="W55">
-        <v>0.2345530762920427</v>
+        <v>0.2345761674718196</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.02203356848949212</v>
+        <v>0.02162553944339041</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6332,22 +6332,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1976845383665509</v>
+        <v>0.1995845383665509</v>
       </c>
       <c r="C56">
-        <v>-7.391875643523633</v>
+        <v>-7.963328639348161</v>
       </c>
       <c r="D56">
-        <v>12.74412435647637</v>
+        <v>12.58667136065185</v>
       </c>
       <c r="E56">
-        <v>16.556</v>
+        <v>16.97000000000001</v>
       </c>
       <c r="F56">
-        <v>22.35600000000001</v>
+        <v>22.77000000000001</v>
       </c>
       <c r="G56">
         <v>2.22</v>
@@ -6368,37 +6368,37 @@
         <v>0.114</v>
       </c>
       <c r="M56">
-        <v>5.271544800000002</v>
+        <v>5.369166000000002</v>
       </c>
       <c r="N56">
-        <v>-5.157544800000002</v>
+        <v>-5.255166000000002</v>
       </c>
       <c r="O56">
-        <v>-1.237810752</v>
+        <v>-1.26123984</v>
       </c>
       <c r="P56">
-        <v>-3.919734048000001</v>
+        <v>-3.993926160000001</v>
       </c>
       <c r="Q56">
-        <v>-4.033734048000001</v>
+        <v>-4.107926160000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1543769737647137</v>
+        <v>0.1567897954039296</v>
       </c>
       <c r="T56">
-        <v>1.830763761699811</v>
+        <v>1.871447400848696</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.005190129466413714</v>
+        <v>0.005095763476115283</v>
       </c>
       <c r="W56">
-        <v>0.2345761674718196</v>
+        <v>0.234598418972332</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.02162553944339041</v>
+        <v>0.021232347817147</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6414,22 +6414,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1995845383665509</v>
+        <v>0.2014845383665509</v>
       </c>
       <c r="C57">
-        <v>-7.963328639348161</v>
+        <v>-8.530938470074778</v>
       </c>
       <c r="D57">
-        <v>12.58667136065185</v>
+        <v>12.43306152992523</v>
       </c>
       <c r="E57">
-        <v>16.97000000000001</v>
+        <v>17.384</v>
       </c>
       <c r="F57">
-        <v>22.77000000000001</v>
+        <v>23.184</v>
       </c>
       <c r="G57">
         <v>2.22</v>
@@ -6450,37 +6450,37 @@
         <v>0.114</v>
       </c>
       <c r="M57">
-        <v>5.369166000000002</v>
+        <v>5.466787200000002</v>
       </c>
       <c r="N57">
-        <v>-5.255166000000002</v>
+        <v>-5.352787200000002</v>
       </c>
       <c r="O57">
-        <v>-1.26123984</v>
+        <v>-1.284668928</v>
       </c>
       <c r="P57">
-        <v>-3.993926160000001</v>
+        <v>-4.068118272000001</v>
       </c>
       <c r="Q57">
-        <v>-4.107926160000002</v>
+        <v>-4.182118272000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1567897954039296</v>
+        <v>0.1593122907540189</v>
       </c>
       <c r="T57">
-        <v>1.871447400848696</v>
+        <v>1.913980296322531</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.005095763476115283</v>
+        <v>0.005004767699756082</v>
       </c>
       <c r="W57">
-        <v>0.234598418972332</v>
+        <v>0.2346198757763975</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.021232347817147</v>
+        <v>0.02085319874898361</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6496,22 +6496,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2014845383665509</v>
+        <v>0.2033845383665509</v>
       </c>
       <c r="C58">
-        <v>-8.530938470074778</v>
+        <v>-9.094844147063915</v>
       </c>
       <c r="D58">
-        <v>12.43306152992523</v>
+        <v>12.28315585293609</v>
       </c>
       <c r="E58">
-        <v>17.384</v>
+        <v>17.79800000000001</v>
       </c>
       <c r="F58">
-        <v>23.184</v>
+        <v>23.59800000000001</v>
       </c>
       <c r="G58">
         <v>2.22</v>
@@ -6532,37 +6532,37 @@
         <v>0.114</v>
       </c>
       <c r="M58">
-        <v>5.466787200000002</v>
+        <v>5.564408400000001</v>
       </c>
       <c r="N58">
-        <v>-5.352787200000002</v>
+        <v>-5.450408400000001</v>
       </c>
       <c r="O58">
-        <v>-1.284668928</v>
+        <v>-1.308098016</v>
       </c>
       <c r="P58">
-        <v>-4.068118272000001</v>
+        <v>-4.142310384000001</v>
       </c>
       <c r="Q58">
-        <v>-4.182118272000001</v>
+        <v>-4.256310384000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1593122907540189</v>
+        <v>0.1619521114692286</v>
       </c>
       <c r="T58">
-        <v>1.913980296322531</v>
+        <v>1.958491466004449</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.005004767699756082</v>
+        <v>0.004916964757655098</v>
       </c>
       <c r="W58">
-        <v>0.2346198757763975</v>
+        <v>0.2346405797101449</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.02085319874898361</v>
+        <v>0.0204873531568962</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6578,22 +6578,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2033845383665509</v>
+        <v>0.2052845383665509</v>
       </c>
       <c r="C59">
-        <v>-9.094844147063915</v>
+        <v>-9.655178057295016</v>
       </c>
       <c r="D59">
-        <v>12.28315585293609</v>
+        <v>12.13682194270499</v>
       </c>
       <c r="E59">
-        <v>17.79800000000001</v>
+        <v>18.21200000000001</v>
       </c>
       <c r="F59">
-        <v>23.59800000000001</v>
+        <v>24.01200000000001</v>
       </c>
       <c r="G59">
         <v>2.22</v>
@@ -6614,37 +6614,37 @@
         <v>0.114</v>
       </c>
       <c r="M59">
-        <v>5.564408400000001</v>
+        <v>5.662029600000002</v>
       </c>
       <c r="N59">
-        <v>-5.450408400000001</v>
+        <v>-5.548029600000002</v>
       </c>
       <c r="O59">
-        <v>-1.308098016</v>
+        <v>-1.331527104000001</v>
       </c>
       <c r="P59">
-        <v>-4.142310384000001</v>
+        <v>-4.216502496000002</v>
       </c>
       <c r="Q59">
-        <v>-4.256310384000001</v>
+        <v>-4.330502496000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1619521114692286</v>
+        <v>0.1647176379327817</v>
       </c>
       <c r="T59">
-        <v>1.958491466004449</v>
+        <v>2.005122215195032</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.004916964757655098</v>
+        <v>0.004832189503212768</v>
       </c>
       <c r="W59">
-        <v>0.2346405797101449</v>
+        <v>0.2346605697151425</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.0204873531568962</v>
+        <v>0.02013412293005323</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6660,22 +6660,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2052845383665509</v>
+        <v>0.2071845383665509</v>
       </c>
       <c r="C60">
-        <v>-9.655178057295005</v>
+        <v>-10.21206635331481</v>
       </c>
       <c r="D60">
-        <v>12.13682194270499</v>
+        <v>11.99393364668519</v>
       </c>
       <c r="E60">
-        <v>18.212</v>
+        <v>18.626</v>
       </c>
       <c r="F60">
-        <v>24.012</v>
+        <v>24.426</v>
       </c>
       <c r="G60">
         <v>2.22</v>
@@ -6696,37 +6696,37 @@
         <v>0.114</v>
       </c>
       <c r="M60">
-        <v>5.6620296</v>
+        <v>5.759650800000001</v>
       </c>
       <c r="N60">
-        <v>-5.5480296</v>
+        <v>-5.645650800000001</v>
       </c>
       <c r="O60">
-        <v>-1.331527104</v>
+        <v>-1.354956192</v>
       </c>
       <c r="P60">
-        <v>-4.216502496</v>
+        <v>-4.290694608000001</v>
       </c>
       <c r="Q60">
-        <v>-4.330502496</v>
+        <v>-4.404694608000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1647176379327817</v>
+        <v>0.1676180681262641</v>
       </c>
       <c r="T60">
-        <v>2.005122215195032</v>
+        <v>2.054027635077837</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.00483218950321277</v>
+        <v>0.004750287986209163</v>
       </c>
       <c r="W60">
-        <v>0.2346605697151425</v>
+        <v>0.2346798820928519</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.02013412293005323</v>
+        <v>0.01979286660920487</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6742,22 +6742,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2071845383665509</v>
+        <v>0.2090845383665509</v>
       </c>
       <c r="C61">
-        <v>-10.21206635331481</v>
+        <v>-10.7656293159607</v>
       </c>
       <c r="D61">
-        <v>11.99393364668519</v>
+        <v>11.8543706840393</v>
       </c>
       <c r="E61">
-        <v>18.626</v>
+        <v>19.04</v>
       </c>
       <c r="F61">
-        <v>24.426</v>
+        <v>24.84</v>
       </c>
       <c r="G61">
         <v>2.22</v>
@@ -6778,37 +6778,37 @@
         <v>0.114</v>
       </c>
       <c r="M61">
-        <v>5.759650800000001</v>
+        <v>5.857272000000001</v>
       </c>
       <c r="N61">
-        <v>-5.645650800000001</v>
+        <v>-5.743272000000001</v>
       </c>
       <c r="O61">
-        <v>-1.354956192</v>
+        <v>-1.37838528</v>
       </c>
       <c r="P61">
-        <v>-4.290694608000001</v>
+        <v>-4.364886720000001</v>
       </c>
       <c r="Q61">
-        <v>-4.404694608000001</v>
+        <v>-4.478886720000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1676180681262641</v>
+        <v>0.1706635198294207</v>
       </c>
       <c r="T61">
-        <v>2.054027635077837</v>
+        <v>2.105378325954783</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.004750287986209163</v>
+        <v>0.004671116519772344</v>
       </c>
       <c r="W61">
-        <v>0.2346798820928519</v>
+        <v>0.2346985507246377</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.01979286660920487</v>
+        <v>0.01946298549905146</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6824,22 +6824,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2090845383665509</v>
+        <v>0.2109845383665509</v>
       </c>
       <c r="C62">
-        <v>-10.7656293159607</v>
+        <v>-11.3159816920511</v>
       </c>
       <c r="D62">
-        <v>11.8543706840393</v>
+        <v>11.7180183079489</v>
       </c>
       <c r="E62">
-        <v>19.04</v>
+        <v>19.454</v>
       </c>
       <c r="F62">
-        <v>24.84</v>
+        <v>25.254</v>
       </c>
       <c r="G62">
         <v>2.22</v>
@@ -6860,37 +6860,37 @@
         <v>0.114</v>
       </c>
       <c r="M62">
-        <v>5.857272000000001</v>
+        <v>5.954893200000001</v>
       </c>
       <c r="N62">
-        <v>-5.743272000000001</v>
+        <v>-5.840893200000001</v>
       </c>
       <c r="O62">
-        <v>-1.37838528</v>
+        <v>-1.401814368</v>
       </c>
       <c r="P62">
-        <v>-4.364886720000001</v>
+        <v>-4.439078832000001</v>
       </c>
       <c r="Q62">
-        <v>-4.478886720000001</v>
+        <v>-4.553078832000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1706635198294207</v>
+        <v>0.1738651485429956</v>
       </c>
       <c r="T62">
-        <v>2.105378325954783</v>
+        <v>2.159362385594649</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.004671116519772344</v>
+        <v>0.004594540839120338</v>
       </c>
       <c r="W62">
-        <v>0.2346985507246377</v>
+        <v>0.2347166072701354</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.01946298549905146</v>
+        <v>0.01914392016300137</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6906,22 +6906,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2109845383665509</v>
+        <v>0.2128845383665509</v>
       </c>
       <c r="C63">
-        <v>-11.3159816920511</v>
+        <v>-11.86323300903568</v>
       </c>
       <c r="D63">
-        <v>11.7180183079489</v>
+        <v>11.58476699096433</v>
       </c>
       <c r="E63">
-        <v>19.454</v>
+        <v>19.868</v>
       </c>
       <c r="F63">
-        <v>25.254</v>
+        <v>25.668</v>
       </c>
       <c r="G63">
         <v>2.22</v>
@@ -6942,37 +6942,37 @@
         <v>0.114</v>
       </c>
       <c r="M63">
-        <v>5.954893200000001</v>
+        <v>6.052514400000001</v>
       </c>
       <c r="N63">
-        <v>-5.840893200000001</v>
+        <v>-5.938514400000001</v>
       </c>
       <c r="O63">
-        <v>-1.401814368</v>
+        <v>-1.425243456</v>
       </c>
       <c r="P63">
-        <v>-4.439078832000001</v>
+        <v>-4.513270944</v>
       </c>
       <c r="Q63">
-        <v>-4.553078832000001</v>
+        <v>-4.627270944</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1738651485429956</v>
+        <v>0.1772352840309692</v>
       </c>
       <c r="T63">
-        <v>2.159362385594649</v>
+        <v>2.21618771153135</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.004594540839120338</v>
+        <v>0.004520435341715172</v>
       </c>
       <c r="W63">
-        <v>0.2347166072701354</v>
+        <v>0.2347340813464236</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.01914392016300137</v>
+        <v>0.01883514725714652</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6988,22 +6988,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2128845383665509</v>
+        <v>0.2147845383665509</v>
       </c>
       <c r="C64">
-        <v>-11.86323300903568</v>
+        <v>-12.40748786841865</v>
       </c>
       <c r="D64">
-        <v>11.58476699096433</v>
+        <v>11.45451213158135</v>
       </c>
       <c r="E64">
-        <v>19.868</v>
+        <v>20.282</v>
       </c>
       <c r="F64">
-        <v>25.668</v>
+        <v>26.082</v>
       </c>
       <c r="G64">
         <v>2.22</v>
@@ -7024,37 +7024,37 @@
         <v>0.114</v>
       </c>
       <c r="M64">
-        <v>6.052514400000001</v>
+        <v>6.150135600000001</v>
       </c>
       <c r="N64">
-        <v>-5.938514400000001</v>
+        <v>-6.036135600000001</v>
       </c>
       <c r="O64">
-        <v>-1.425243456</v>
+        <v>-1.448672544</v>
       </c>
       <c r="P64">
-        <v>-4.513270944</v>
+        <v>-4.587463056000001</v>
       </c>
       <c r="Q64">
-        <v>-4.627270944</v>
+        <v>-4.701463056000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1772352840309692</v>
+        <v>0.1807875890047792</v>
       </c>
       <c r="T64">
-        <v>2.21618771153135</v>
+        <v>2.276084676707873</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.004520435341715172</v>
+        <v>0.004448682399783185</v>
       </c>
       <c r="W64">
-        <v>0.2347340813464236</v>
+        <v>0.2347510006901311</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.01883514725714652</v>
+        <v>0.01853617666576324</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7070,22 +7070,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2147845383665509</v>
+        <v>0.2166845383665509</v>
       </c>
       <c r="C65">
-        <v>-12.40748786841865</v>
+        <v>-12.94884621960735</v>
       </c>
       <c r="D65">
-        <v>11.45451213158135</v>
+        <v>11.32715378039266</v>
       </c>
       <c r="E65">
-        <v>20.282</v>
+        <v>20.69600000000001</v>
       </c>
       <c r="F65">
-        <v>26.082</v>
+        <v>26.49600000000001</v>
       </c>
       <c r="G65">
         <v>2.22</v>
@@ -7106,37 +7106,37 @@
         <v>0.114</v>
       </c>
       <c r="M65">
-        <v>6.150135600000001</v>
+        <v>6.247756800000001</v>
       </c>
       <c r="N65">
-        <v>-6.036135600000001</v>
+        <v>-6.133756800000001</v>
       </c>
       <c r="O65">
-        <v>-1.448672544</v>
+        <v>-1.472101632</v>
       </c>
       <c r="P65">
-        <v>-4.587463056000001</v>
+        <v>-4.661655168000001</v>
       </c>
       <c r="Q65">
-        <v>-4.701463056000001</v>
+        <v>-4.775655168000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1807875890047792</v>
+        <v>0.184537244254912</v>
       </c>
       <c r="T65">
-        <v>2.276084676707873</v>
+        <v>2.33930925106087</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.004448682399783185</v>
+        <v>0.004379171737286572</v>
       </c>
       <c r="W65">
-        <v>0.2347510006901311</v>
+        <v>0.2347673913043478</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.01853617666576324</v>
+        <v>0.0182465489053607</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7152,22 +7152,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2166845383665509</v>
+        <v>0.218584538366551</v>
       </c>
       <c r="C66">
-        <v>-12.94884621960735</v>
+        <v>-13.48740361569269</v>
       </c>
       <c r="D66">
-        <v>11.32715378039266</v>
+        <v>11.20259638430731</v>
       </c>
       <c r="E66">
-        <v>20.69600000000001</v>
+        <v>21.11</v>
       </c>
       <c r="F66">
-        <v>26.49600000000001</v>
+        <v>26.91</v>
       </c>
       <c r="G66">
         <v>2.22</v>
@@ -7188,37 +7188,37 @@
         <v>0.114</v>
       </c>
       <c r="M66">
-        <v>6.247756800000001</v>
+        <v>6.345378000000001</v>
       </c>
       <c r="N66">
-        <v>-6.133756800000001</v>
+        <v>-6.231378000000001</v>
       </c>
       <c r="O66">
-        <v>-1.472101632</v>
+        <v>-1.49553072</v>
       </c>
       <c r="P66">
-        <v>-4.661655168000001</v>
+        <v>-4.735847280000001</v>
       </c>
       <c r="Q66">
-        <v>-4.775655168000001</v>
+        <v>-4.849847280000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.184537244254912</v>
+        <v>0.188501165519338</v>
       </c>
       <c r="T66">
-        <v>2.33930925106087</v>
+        <v>2.406146658234038</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.004379171737286572</v>
+        <v>0.00431179986440524</v>
       </c>
       <c r="W66">
-        <v>0.2347673913043478</v>
+        <v>0.2347832775919733</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.0182465489053607</v>
+        <v>0.01796583276835517</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7234,22 +7234,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.218584538366551</v>
+        <v>0.2204845383665509</v>
       </c>
       <c r="C67">
-        <v>-13.48740361569269</v>
+        <v>-14.02325145253742</v>
       </c>
       <c r="D67">
-        <v>11.20259638430731</v>
+        <v>11.08074854746258</v>
       </c>
       <c r="E67">
-        <v>21.11</v>
+        <v>21.524</v>
       </c>
       <c r="F67">
-        <v>26.91</v>
+        <v>27.32400000000001</v>
       </c>
       <c r="G67">
         <v>2.22</v>
@@ -7270,37 +7270,37 @@
         <v>0.114</v>
       </c>
       <c r="M67">
-        <v>6.345378000000001</v>
+        <v>6.442999200000002</v>
       </c>
       <c r="N67">
-        <v>-6.231378000000001</v>
+        <v>-6.328999200000002</v>
       </c>
       <c r="O67">
-        <v>-1.49553072</v>
+        <v>-1.518959808</v>
       </c>
       <c r="P67">
-        <v>-4.735847280000001</v>
+        <v>-4.810039392000002</v>
       </c>
       <c r="Q67">
-        <v>-4.849847280000001</v>
+        <v>-4.924039392000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.188501165519338</v>
+        <v>0.192698258622848</v>
       </c>
       <c r="T67">
-        <v>2.406146658234038</v>
+        <v>2.476915677593862</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.00431179986440524</v>
+        <v>0.004246469563429403</v>
       </c>
       <c r="W67">
-        <v>0.2347832775919733</v>
+        <v>0.2347986824769434</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.01796583276835517</v>
+        <v>0.0176936231809558</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7316,22 +7316,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2204845383665509</v>
+        <v>0.2223845383665509</v>
       </c>
       <c r="C68">
-        <v>-14.02325145253742</v>
+        <v>-14.55647719242907</v>
       </c>
       <c r="D68">
-        <v>11.08074854746258</v>
+        <v>10.96152280757093</v>
       </c>
       <c r="E68">
-        <v>21.524</v>
+        <v>21.93800000000001</v>
       </c>
       <c r="F68">
-        <v>27.32400000000001</v>
+        <v>27.73800000000001</v>
       </c>
       <c r="G68">
         <v>2.22</v>
@@ -7352,37 +7352,37 @@
         <v>0.114</v>
       </c>
       <c r="M68">
-        <v>6.442999200000002</v>
+        <v>6.540620400000002</v>
       </c>
       <c r="N68">
-        <v>-6.328999200000002</v>
+        <v>-6.426620400000002</v>
       </c>
       <c r="O68">
-        <v>-1.518959808</v>
+        <v>-1.542388896</v>
       </c>
       <c r="P68">
-        <v>-4.810039392000002</v>
+        <v>-4.884231504000002</v>
       </c>
       <c r="Q68">
-        <v>-4.924039392000002</v>
+        <v>-4.998231504000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.192698258622848</v>
+        <v>0.1971497210053585</v>
       </c>
       <c r="T68">
-        <v>2.476915677593862</v>
+        <v>2.551973728430041</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.004246469563429403</v>
+        <v>0.004183089420691651</v>
       </c>
       <c r="W68">
-        <v>0.2347986824769434</v>
+        <v>0.2348136275146009</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7390,7 +7390,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.0176936231809558</v>
+        <v>0.01742953925288182</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7398,22 +7398,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2223845383665509</v>
+        <v>0.2242845383665509</v>
       </c>
       <c r="C69">
-        <v>-14.55647719242907</v>
+        <v>-15.08716457344811</v>
       </c>
       <c r="D69">
-        <v>10.96152280757093</v>
+        <v>10.84483542655189</v>
       </c>
       <c r="E69">
-        <v>21.93800000000001</v>
+        <v>22.352</v>
       </c>
       <c r="F69">
-        <v>27.73800000000001</v>
+        <v>28.152</v>
       </c>
       <c r="G69">
         <v>2.22</v>
@@ -7434,37 +7434,37 @@
         <v>0.114</v>
       </c>
       <c r="M69">
-        <v>6.540620400000002</v>
+        <v>6.638241600000002</v>
       </c>
       <c r="N69">
-        <v>-6.426620400000002</v>
+        <v>-6.524241600000002</v>
       </c>
       <c r="O69">
-        <v>-1.542388896</v>
+        <v>-1.565817984</v>
       </c>
       <c r="P69">
-        <v>-4.884231504000002</v>
+        <v>-4.958423616000001</v>
       </c>
       <c r="Q69">
-        <v>-4.998231504000001</v>
+        <v>-5.072423616000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1971497210053585</v>
+        <v>0.201879399786776</v>
       </c>
       <c r="T69">
-        <v>2.551973728430041</v>
+        <v>2.631722907443479</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.004183089420691651</v>
+        <v>0.004121573399799127</v>
       </c>
       <c r="W69">
-        <v>0.2348136275146009</v>
+        <v>0.2348281329923274</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.01742953925288182</v>
+        <v>0.01717322249916298</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7480,22 +7480,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2242845383665509</v>
+        <v>0.2261845383665509</v>
       </c>
       <c r="C70">
-        <v>-15.08716457344811</v>
+        <v>-15.61539380560424</v>
       </c>
       <c r="D70">
-        <v>10.84483542655189</v>
+        <v>10.73060619439577</v>
       </c>
       <c r="E70">
-        <v>22.352</v>
+        <v>22.76600000000001</v>
       </c>
       <c r="F70">
-        <v>28.152</v>
+        <v>28.56600000000001</v>
       </c>
       <c r="G70">
         <v>2.22</v>
@@ -7516,37 +7516,37 @@
         <v>0.114</v>
       </c>
       <c r="M70">
-        <v>6.638241600000002</v>
+        <v>6.735862800000001</v>
       </c>
       <c r="N70">
-        <v>-6.524241600000002</v>
+        <v>-6.621862800000001</v>
       </c>
       <c r="O70">
-        <v>-1.565817984</v>
+        <v>-1.589247072</v>
       </c>
       <c r="P70">
-        <v>-4.958423616000001</v>
+        <v>-5.032615728000001</v>
       </c>
       <c r="Q70">
-        <v>-5.072423616000001</v>
+        <v>-5.146615728000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.201879399786776</v>
+        <v>0.2069142191347365</v>
       </c>
       <c r="T70">
-        <v>2.631722907443479</v>
+        <v>2.716617194780366</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.004121573399799127</v>
+        <v>0.00406184045197595</v>
       </c>
       <c r="W70">
-        <v>0.2348281329923274</v>
+        <v>0.2348422180214241</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.01717322249916298</v>
+        <v>0.01692433521656644</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7562,22 +7562,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2261845383665509</v>
+        <v>0.2280845383665509</v>
       </c>
       <c r="C71">
-        <v>-15.61539380560424</v>
+        <v>-16.14124175470651</v>
       </c>
       <c r="D71">
-        <v>10.73060619439577</v>
+        <v>10.61875824529349</v>
       </c>
       <c r="E71">
-        <v>22.76600000000001</v>
+        <v>23.18000000000001</v>
       </c>
       <c r="F71">
-        <v>28.56600000000001</v>
+        <v>28.98000000000001</v>
       </c>
       <c r="G71">
         <v>2.22</v>
@@ -7598,37 +7598,37 @@
         <v>0.114</v>
       </c>
       <c r="M71">
-        <v>6.735862800000001</v>
+        <v>6.833484000000002</v>
       </c>
       <c r="N71">
-        <v>-6.621862800000001</v>
+        <v>-6.719484000000002</v>
       </c>
       <c r="O71">
-        <v>-1.589247072</v>
+        <v>-1.612676160000001</v>
       </c>
       <c r="P71">
-        <v>-5.032615728000001</v>
+        <v>-5.106807840000002</v>
       </c>
       <c r="Q71">
-        <v>-5.146615728000001</v>
+        <v>-5.220807840000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2069142191347365</v>
+        <v>0.2122846931058944</v>
       </c>
       <c r="T71">
-        <v>2.716617194780366</v>
+        <v>2.807171101273044</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.00406184045197595</v>
+        <v>0.004003814159804866</v>
       </c>
       <c r="W71">
-        <v>0.2348422180214241</v>
+        <v>0.234855900621118</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.01692433521656644</v>
+        <v>0.01668255899918691</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7644,22 +7644,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2280845383665509</v>
+        <v>0.2299845383665509</v>
       </c>
       <c r="C72">
-        <v>-16.14124175470651</v>
+        <v>-16.66478211485283</v>
       </c>
       <c r="D72">
-        <v>10.61875824529349</v>
+        <v>10.50921788514717</v>
       </c>
       <c r="E72">
-        <v>23.18000000000001</v>
+        <v>23.594</v>
       </c>
       <c r="F72">
-        <v>28.98000000000001</v>
+        <v>29.39400000000001</v>
       </c>
       <c r="G72">
         <v>2.22</v>
@@ -7680,37 +7680,37 @@
         <v>0.114</v>
       </c>
       <c r="M72">
-        <v>6.833484000000002</v>
+        <v>6.931105200000002</v>
       </c>
       <c r="N72">
-        <v>-6.719484000000002</v>
+        <v>-6.817105200000002</v>
       </c>
       <c r="O72">
-        <v>-1.612676160000001</v>
+        <v>-1.636105248</v>
       </c>
       <c r="P72">
-        <v>-5.106807840000002</v>
+        <v>-5.180999952000001</v>
       </c>
       <c r="Q72">
-        <v>-5.220807840000002</v>
+        <v>-5.294999952000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2122846931058944</v>
+        <v>0.2180255445923045</v>
       </c>
       <c r="T72">
-        <v>2.807171101273044</v>
+        <v>2.903970104765219</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.004003814159804866</v>
+        <v>0.00394742241107522</v>
       </c>
       <c r="W72">
-        <v>0.234855900621118</v>
+        <v>0.2348691977954685</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.01668255899918691</v>
+        <v>0.0164475933794801</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7726,22 +7726,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2299845383665509</v>
+        <v>0.2318845383665509</v>
       </c>
       <c r="C73">
-        <v>-16.66478211485283</v>
+        <v>-17.18608557035243</v>
       </c>
       <c r="D73">
-        <v>10.50921788514717</v>
+        <v>10.40191442964757</v>
       </c>
       <c r="E73">
-        <v>23.594</v>
+        <v>24.008</v>
       </c>
       <c r="F73">
-        <v>29.394</v>
+        <v>29.808</v>
       </c>
       <c r="G73">
         <v>2.22</v>
@@ -7762,37 +7762,37 @@
         <v>0.114</v>
       </c>
       <c r="M73">
-        <v>6.931105200000001</v>
+        <v>7.028726400000001</v>
       </c>
       <c r="N73">
-        <v>-6.817105200000001</v>
+        <v>-6.914726400000001</v>
       </c>
       <c r="O73">
-        <v>-1.636105248</v>
+        <v>-1.659534336</v>
       </c>
       <c r="P73">
-        <v>-5.180999952000001</v>
+        <v>-5.255192064000001</v>
       </c>
       <c r="Q73">
-        <v>-5.294999952</v>
+        <v>-5.369192064000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2180255445923045</v>
+        <v>0.2241764568991725</v>
       </c>
       <c r="T73">
-        <v>2.903970104765218</v>
+        <v>3.007683322792547</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.00394742241107522</v>
+        <v>0.003892597099810287</v>
       </c>
       <c r="W73">
-        <v>0.2348691977954685</v>
+        <v>0.2348821256038648</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.0164475933794801</v>
+        <v>0.01621915458254286</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7808,22 +7808,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2318845383665509</v>
+        <v>0.2337845383665509</v>
       </c>
       <c r="C74">
-        <v>-17.18608557035243</v>
+        <v>-17.7052199478287</v>
       </c>
       <c r="D74">
-        <v>10.40191442964757</v>
+        <v>10.2967800521713</v>
       </c>
       <c r="E74">
-        <v>24.008</v>
+        <v>24.422</v>
       </c>
       <c r="F74">
-        <v>29.808</v>
+        <v>30.222</v>
       </c>
       <c r="G74">
         <v>2.22</v>
@@ -7844,37 +7844,37 @@
         <v>0.114</v>
       </c>
       <c r="M74">
-        <v>7.028726400000001</v>
+        <v>7.126347600000002</v>
       </c>
       <c r="N74">
-        <v>-6.914726400000001</v>
+        <v>-7.012347600000002</v>
       </c>
       <c r="O74">
-        <v>-1.659534336</v>
+        <v>-1.682963424</v>
       </c>
       <c r="P74">
-        <v>-5.255192064000001</v>
+        <v>-5.329384176000001</v>
       </c>
       <c r="Q74">
-        <v>-5.369192064000001</v>
+        <v>-5.443384176000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2241764568991725</v>
+        <v>0.2307829923398826</v>
       </c>
       <c r="T74">
-        <v>3.007683322792547</v>
+        <v>3.119079001414493</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.003892597099810287</v>
+        <v>0.00383927385186768</v>
       </c>
       <c r="W74">
-        <v>0.2348821256038648</v>
+        <v>0.2348946992257296</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.01621915458254286</v>
+        <v>0.01599697438278203</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7890,22 +7890,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2337845383665509</v>
+        <v>0.2356845383665509</v>
       </c>
       <c r="C75">
-        <v>-17.7052199478287</v>
+        <v>-18.22225035919036</v>
       </c>
       <c r="D75">
-        <v>10.2967800521713</v>
+        <v>10.19374964080964</v>
       </c>
       <c r="E75">
-        <v>24.422</v>
+        <v>24.836</v>
       </c>
       <c r="F75">
-        <v>30.222</v>
+        <v>30.636</v>
       </c>
       <c r="G75">
         <v>2.22</v>
@@ -7926,37 +7926,37 @@
         <v>0.114</v>
       </c>
       <c r="M75">
-        <v>7.126347600000002</v>
+        <v>7.223968800000001</v>
       </c>
       <c r="N75">
-        <v>-7.012347600000002</v>
+        <v>-7.109968800000001</v>
       </c>
       <c r="O75">
-        <v>-1.682963424</v>
+        <v>-1.706392512</v>
       </c>
       <c r="P75">
-        <v>-5.329384176000001</v>
+        <v>-5.403576288000001</v>
       </c>
       <c r="Q75">
-        <v>-5.443384176000001</v>
+        <v>-5.517576288000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2307829923398826</v>
+        <v>0.2378977228144935</v>
       </c>
       <c r="T75">
-        <v>3.119079001414493</v>
+        <v>3.239043578391974</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.00383927385186768</v>
+        <v>0.003787391772788387</v>
       </c>
       <c r="W75">
-        <v>0.2348946992257296</v>
+        <v>0.2349069330199765</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.01599697438278203</v>
+        <v>0.01578079905328489</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7972,22 +7972,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2356845383665509</v>
+        <v>0.2375845383665509</v>
       </c>
       <c r="C76">
-        <v>-18.22225035919036</v>
+        <v>-18.73723933610425</v>
       </c>
       <c r="D76">
-        <v>10.19374964080964</v>
+        <v>10.09276066389576</v>
       </c>
       <c r="E76">
-        <v>24.836</v>
+        <v>25.25</v>
       </c>
       <c r="F76">
-        <v>30.636</v>
+        <v>31.05</v>
       </c>
       <c r="G76">
         <v>2.22</v>
@@ -8008,37 +8008,37 @@
         <v>0.114</v>
       </c>
       <c r="M76">
-        <v>7.223968800000001</v>
+        <v>7.321590000000001</v>
       </c>
       <c r="N76">
-        <v>-7.109968800000001</v>
+        <v>-7.207590000000001</v>
       </c>
       <c r="O76">
-        <v>-1.706392512</v>
+        <v>-1.7298216</v>
       </c>
       <c r="P76">
-        <v>-5.403576288000001</v>
+        <v>-5.477768400000001</v>
       </c>
       <c r="Q76">
-        <v>-5.517576288000001</v>
+        <v>-5.591768400000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2378977228144935</v>
+        <v>0.2455816317270732</v>
       </c>
       <c r="T76">
-        <v>3.239043578391974</v>
+        <v>3.368605321527653</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.003787391772788387</v>
+        <v>0.003736893215817875</v>
       </c>
       <c r="W76">
-        <v>0.2349069330199765</v>
+        <v>0.2349188405797102</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.01578079905328489</v>
+        <v>0.01557038839924108</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8054,22 +8054,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2375845383665509</v>
+        <v>0.2394845383665509</v>
       </c>
       <c r="C77">
-        <v>-18.73723933610425</v>
+        <v>-19.25024695655308</v>
       </c>
       <c r="D77">
-        <v>10.09276066389576</v>
+        <v>9.993753043446928</v>
       </c>
       <c r="E77">
-        <v>25.25</v>
+        <v>25.66400000000001</v>
       </c>
       <c r="F77">
-        <v>31.05</v>
+        <v>31.46400000000001</v>
       </c>
       <c r="G77">
         <v>2.22</v>
@@ -8090,37 +8090,37 @@
         <v>0.114</v>
       </c>
       <c r="M77">
-        <v>7.321590000000001</v>
+        <v>7.419211200000001</v>
       </c>
       <c r="N77">
-        <v>-7.207590000000001</v>
+        <v>-7.305211200000001</v>
       </c>
       <c r="O77">
-        <v>-1.7298216</v>
+        <v>-1.753250688</v>
       </c>
       <c r="P77">
-        <v>-5.477768400000001</v>
+        <v>-5.551960512000001</v>
       </c>
       <c r="Q77">
-        <v>-5.591768400000001</v>
+        <v>-5.665960512000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2455816317270732</v>
+        <v>0.2539058663823679</v>
       </c>
       <c r="T77">
-        <v>3.368605321527653</v>
+        <v>3.508963876591305</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.003736893215817875</v>
+        <v>0.003687723568241324</v>
       </c>
       <c r="W77">
-        <v>0.2349188405797102</v>
+        <v>0.2349304347826087</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.01557038839924108</v>
+        <v>0.01536551486767213</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8136,22 +8136,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2394845383665509</v>
+        <v>0.2413845383665509</v>
       </c>
       <c r="C78">
-        <v>-19.25024695655308</v>
+        <v>-19.76133096401671</v>
       </c>
       <c r="D78">
-        <v>9.993753043446928</v>
+        <v>9.896669035983296</v>
       </c>
       <c r="E78">
-        <v>25.66400000000001</v>
+        <v>26.078</v>
       </c>
       <c r="F78">
-        <v>31.46400000000001</v>
+        <v>31.878</v>
       </c>
       <c r="G78">
         <v>2.22</v>
@@ -8172,37 +8172,37 @@
         <v>0.114</v>
       </c>
       <c r="M78">
-        <v>7.419211200000001</v>
+        <v>7.516832400000001</v>
       </c>
       <c r="N78">
-        <v>-7.305211200000001</v>
+        <v>-7.402832400000001</v>
       </c>
       <c r="O78">
-        <v>-1.753250688</v>
+        <v>-1.776679776</v>
       </c>
       <c r="P78">
-        <v>-5.551960512000001</v>
+        <v>-5.626152624000001</v>
       </c>
       <c r="Q78">
-        <v>-5.665960512000001</v>
+        <v>-5.740152624000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2539058663823679</v>
+        <v>0.2629539475294274</v>
       </c>
       <c r="T78">
-        <v>3.508963876591305</v>
+        <v>3.661527523399622</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.003687723568241324</v>
+        <v>0.00363983105436806</v>
       </c>
       <c r="W78">
-        <v>0.2349304347826087</v>
+        <v>0.23494172783738</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.01536551486767213</v>
+        <v>0.01516596272653359</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8218,22 +8218,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2413845383665509</v>
+        <v>0.2432845383665509</v>
       </c>
       <c r="C79">
-        <v>-19.76133096401671</v>
+        <v>-20.27054687977346</v>
       </c>
       <c r="D79">
-        <v>9.896669035983296</v>
+        <v>9.801453120226554</v>
       </c>
       <c r="E79">
-        <v>26.078</v>
+        <v>26.49200000000001</v>
       </c>
       <c r="F79">
-        <v>31.878</v>
+        <v>32.29200000000001</v>
       </c>
       <c r="G79">
         <v>2.22</v>
@@ -8254,37 +8254,37 @@
         <v>0.114</v>
       </c>
       <c r="M79">
-        <v>7.516832400000001</v>
+        <v>7.614453600000003</v>
       </c>
       <c r="N79">
-        <v>-7.402832400000001</v>
+        <v>-7.500453600000003</v>
       </c>
       <c r="O79">
-        <v>-1.776679776</v>
+        <v>-1.800108864000001</v>
       </c>
       <c r="P79">
-        <v>-5.626152624000001</v>
+        <v>-5.700344736000002</v>
       </c>
       <c r="Q79">
-        <v>-5.740152624000001</v>
+        <v>-5.814344736000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2629539475294274</v>
+        <v>0.2728245815080378</v>
       </c>
       <c r="T79">
-        <v>3.661527523399622</v>
+        <v>3.827960592645061</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.00363983105436806</v>
+        <v>0.003593166553671033</v>
       </c>
       <c r="W79">
-        <v>0.23494172783738</v>
+        <v>0.2349527313266444</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.01516596272653359</v>
+        <v>0.01497152730696261</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8300,22 +8300,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2432845383665509</v>
+        <v>0.2451845383665509</v>
       </c>
       <c r="C80">
-        <v>-20.27054687977346</v>
+        <v>-20.77794810878045</v>
       </c>
       <c r="D80">
-        <v>9.801453120226554</v>
+        <v>9.708051891219553</v>
       </c>
       <c r="E80">
-        <v>26.49200000000001</v>
+        <v>26.906</v>
       </c>
       <c r="F80">
-        <v>32.29200000000001</v>
+        <v>32.706</v>
       </c>
       <c r="G80">
         <v>2.22</v>
@@ -8336,37 +8336,37 @@
         <v>0.114</v>
       </c>
       <c r="M80">
-        <v>7.614453600000003</v>
+        <v>7.712074800000001</v>
       </c>
       <c r="N80">
-        <v>-7.500453600000003</v>
+        <v>-7.598074800000001</v>
       </c>
       <c r="O80">
-        <v>-1.800108864000001</v>
+        <v>-1.823537952</v>
       </c>
       <c r="P80">
-        <v>-5.700344736000002</v>
+        <v>-5.774536848</v>
       </c>
       <c r="Q80">
-        <v>-5.814344736000002</v>
+        <v>-5.888536848</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2728245815080378</v>
+        <v>0.2836352758655634</v>
       </c>
       <c r="T80">
-        <v>3.827960592645061</v>
+        <v>4.010244430390063</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.003593166553671033</v>
+        <v>0.003547683432738489</v>
       </c>
       <c r="W80">
-        <v>0.2349527313266444</v>
+        <v>0.2349634562465603</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.01497152730696261</v>
+        <v>0.01478201430307702</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8382,22 +8382,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2451845383665509</v>
+        <v>0.2470845383665509</v>
       </c>
       <c r="C81">
-        <v>-20.77794810878045</v>
+        <v>-21.28358603955747</v>
       </c>
       <c r="D81">
-        <v>9.708051891219553</v>
+        <v>9.616413960442532</v>
       </c>
       <c r="E81">
-        <v>26.906</v>
+        <v>27.32</v>
       </c>
       <c r="F81">
-        <v>32.706</v>
+        <v>33.12</v>
       </c>
       <c r="G81">
         <v>2.22</v>
@@ -8418,37 +8418,37 @@
         <v>0.114</v>
       </c>
       <c r="M81">
-        <v>7.712074800000001</v>
+        <v>7.809696000000002</v>
       </c>
       <c r="N81">
-        <v>-7.598074800000001</v>
+        <v>-7.695696000000002</v>
       </c>
       <c r="O81">
-        <v>-1.823537952</v>
+        <v>-1.84696704</v>
       </c>
       <c r="P81">
-        <v>-5.774536848</v>
+        <v>-5.848728960000002</v>
       </c>
       <c r="Q81">
-        <v>-5.888536848</v>
+        <v>-5.962728960000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2836352758655634</v>
+        <v>0.2955270396588415</v>
       </c>
       <c r="T81">
-        <v>4.010244430390063</v>
+        <v>4.210756651909567</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.003547683432738489</v>
+        <v>0.003503337389829257</v>
       </c>
       <c r="W81">
-        <v>0.2349634562465603</v>
+        <v>0.2349739130434783</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.01478201430307702</v>
+        <v>0.01459723912428856</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8464,22 +8464,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2470845383665509</v>
+        <v>0.2489845383665509</v>
       </c>
       <c r="C82">
-        <v>-21.28358603955747</v>
+        <v>-21.78751013846641</v>
       </c>
       <c r="D82">
-        <v>9.616413960442532</v>
+        <v>9.526489861533594</v>
       </c>
       <c r="E82">
-        <v>27.32</v>
+        <v>27.73400000000001</v>
       </c>
       <c r="F82">
-        <v>33.12</v>
+        <v>33.53400000000001</v>
       </c>
       <c r="G82">
         <v>2.22</v>
@@ -8500,37 +8500,37 @@
         <v>0.114</v>
       </c>
       <c r="M82">
-        <v>7.809696000000002</v>
+        <v>7.907317200000001</v>
       </c>
       <c r="N82">
-        <v>-7.695696000000002</v>
+        <v>-7.793317200000001</v>
       </c>
       <c r="O82">
-        <v>-1.84696704</v>
+        <v>-1.870396128</v>
       </c>
       <c r="P82">
-        <v>-5.848728960000002</v>
+        <v>-5.922921072000001</v>
       </c>
       <c r="Q82">
-        <v>-5.962728960000002</v>
+        <v>-6.036921072000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2955270396588415</v>
+        <v>0.3086705680619385</v>
       </c>
       <c r="T82">
-        <v>4.210756651909567</v>
+        <v>4.432375423062703</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.003503337389829257</v>
+        <v>0.003460086310942476</v>
       </c>
       <c r="W82">
-        <v>0.2349739130434783</v>
+        <v>0.2349841116478798</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.01459723912428856</v>
+        <v>0.0144170262955936</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8546,22 +8546,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2489845383665509</v>
+        <v>0.2508845383665509</v>
       </c>
       <c r="C83">
-        <v>-21.78751013846641</v>
+        <v>-22.28976803875025</v>
       </c>
       <c r="D83">
-        <v>9.526489861533594</v>
+        <v>9.438231961249754</v>
       </c>
       <c r="E83">
-        <v>27.73400000000001</v>
+        <v>28.14800000000001</v>
       </c>
       <c r="F83">
-        <v>33.53400000000001</v>
+        <v>33.94800000000001</v>
       </c>
       <c r="G83">
         <v>2.22</v>
@@ -8582,37 +8582,37 @@
         <v>0.114</v>
       </c>
       <c r="M83">
-        <v>7.907317200000001</v>
+        <v>8.004938400000002</v>
       </c>
       <c r="N83">
-        <v>-7.793317200000001</v>
+        <v>-7.890938400000002</v>
       </c>
       <c r="O83">
-        <v>-1.870396128</v>
+        <v>-1.893825216</v>
       </c>
       <c r="P83">
-        <v>-5.922921072000001</v>
+        <v>-5.997113184000002</v>
       </c>
       <c r="Q83">
-        <v>-6.036921072000001</v>
+        <v>-6.111113184000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3086705680619385</v>
+        <v>0.323274488509824</v>
       </c>
       <c r="T83">
-        <v>4.432375423062703</v>
+        <v>4.678618502121742</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.003460086310942476</v>
+        <v>0.003417890136418788</v>
       </c>
       <c r="W83">
-        <v>0.2349841116478798</v>
+        <v>0.2349940615058325</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.0144170262955936</v>
+        <v>0.01424120890174496</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8628,22 +8628,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2508845383665509</v>
+        <v>0.2527845383665509</v>
       </c>
       <c r="C84">
-        <v>-22.28976803875025</v>
+        <v>-22.79040562466799</v>
       </c>
       <c r="D84">
-        <v>9.438231961249754</v>
+        <v>9.35159437533202</v>
       </c>
       <c r="E84">
-        <v>28.14800000000001</v>
+        <v>28.56200000000001</v>
       </c>
       <c r="F84">
-        <v>33.94800000000001</v>
+        <v>34.36200000000001</v>
       </c>
       <c r="G84">
         <v>2.22</v>
@@ -8664,37 +8664,37 @@
         <v>0.114</v>
       </c>
       <c r="M84">
-        <v>8.004938400000002</v>
+        <v>8.102559600000003</v>
       </c>
       <c r="N84">
-        <v>-7.890938400000002</v>
+        <v>-7.988559600000003</v>
       </c>
       <c r="O84">
-        <v>-1.893825216</v>
+        <v>-1.917254304000001</v>
       </c>
       <c r="P84">
-        <v>-5.997113184000002</v>
+        <v>-6.071305296000002</v>
       </c>
       <c r="Q84">
-        <v>-6.111113184000001</v>
+        <v>-6.185305296000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.323274488509824</v>
+        <v>0.339596517245696</v>
       </c>
       <c r="T84">
-        <v>4.678618502121742</v>
+        <v>4.953831355187727</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.003417890136418788</v>
+        <v>0.003376710737184826</v>
       </c>
       <c r="W84">
-        <v>0.2349940615058325</v>
+        <v>0.2350037716081718</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.01424120890174496</v>
+        <v>0.01406962807160339</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8710,22 +8710,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2527845383665509</v>
+        <v>0.2546845383665509</v>
       </c>
       <c r="C85">
-        <v>-22.79040562466799</v>
+        <v>-23.2894671110378</v>
       </c>
       <c r="D85">
-        <v>9.35159437533202</v>
+        <v>9.266532888962209</v>
       </c>
       <c r="E85">
-        <v>28.56200000000001</v>
+        <v>28.97600000000001</v>
       </c>
       <c r="F85">
-        <v>34.36200000000001</v>
+        <v>34.77600000000001</v>
       </c>
       <c r="G85">
         <v>2.22</v>
@@ -8746,37 +8746,37 @@
         <v>0.114</v>
       </c>
       <c r="M85">
-        <v>8.102559600000003</v>
+        <v>8.200180800000004</v>
       </c>
       <c r="N85">
-        <v>-7.988559600000003</v>
+        <v>-8.086180800000003</v>
       </c>
       <c r="O85">
-        <v>-1.917254304000001</v>
+        <v>-1.940683392000001</v>
       </c>
       <c r="P85">
-        <v>-6.071305296000002</v>
+        <v>-6.145497408000002</v>
       </c>
       <c r="Q85">
-        <v>-6.185305296000002</v>
+        <v>-6.259497408000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.339596517245696</v>
+        <v>0.357958799573552</v>
       </c>
       <c r="T85">
-        <v>4.953831355187727</v>
+        <v>5.263445814886961</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.003376710737184826</v>
+        <v>0.003336511799837388</v>
       </c>
       <c r="W85">
-        <v>0.2350037716081718</v>
+        <v>0.2350132505175984</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.01406962807160339</v>
+        <v>0.01390213249932259</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8792,22 +8792,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2546845383665509</v>
+        <v>0.2565845383665509</v>
       </c>
       <c r="C86">
-        <v>-23.28946711103779</v>
+        <v>-23.78699511847832</v>
       </c>
       <c r="D86">
-        <v>9.266532888962209</v>
+        <v>9.183004881521684</v>
       </c>
       <c r="E86">
-        <v>28.976</v>
+        <v>29.39</v>
       </c>
       <c r="F86">
-        <v>34.776</v>
+        <v>35.19</v>
       </c>
       <c r="G86">
         <v>2.22</v>
@@ -8828,37 +8828,37 @@
         <v>0.114</v>
       </c>
       <c r="M86">
-        <v>8.200180800000002</v>
+        <v>8.297802000000001</v>
       </c>
       <c r="N86">
-        <v>-8.086180800000001</v>
+        <v>-8.183802</v>
       </c>
       <c r="O86">
-        <v>-1.940683392</v>
+        <v>-1.96411248</v>
       </c>
       <c r="P86">
-        <v>-6.145497408000001</v>
+        <v>-6.21968952</v>
       </c>
       <c r="Q86">
-        <v>-6.259497408000001</v>
+        <v>-6.33368952</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3579587995735518</v>
+        <v>0.3787693862117886</v>
       </c>
       <c r="T86">
-        <v>5.263445814886957</v>
+        <v>5.614342202546087</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.003336511799837388</v>
+        <v>0.003297258719839302</v>
       </c>
       <c r="W86">
-        <v>0.2350132505175984</v>
+        <v>0.2350225063938619</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.01390213249932259</v>
+        <v>0.01373857799933054</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8874,22 +8874,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2565845383665509</v>
+        <v>0.2584845383665509</v>
       </c>
       <c r="C87">
-        <v>-23.78699511847832</v>
+        <v>-24.28303074461688</v>
       </c>
       <c r="D87">
-        <v>9.183004881521684</v>
+        <v>9.100969255383122</v>
       </c>
       <c r="E87">
-        <v>29.39</v>
+        <v>29.80400000000001</v>
       </c>
       <c r="F87">
-        <v>35.19</v>
+        <v>35.60400000000001</v>
       </c>
       <c r="G87">
         <v>2.22</v>
@@ -8910,37 +8910,37 @@
         <v>0.114</v>
       </c>
       <c r="M87">
-        <v>8.297802000000001</v>
+        <v>8.395423200000002</v>
       </c>
       <c r="N87">
-        <v>-8.183802</v>
+        <v>-8.281423200000001</v>
       </c>
       <c r="O87">
-        <v>-1.96411248</v>
+        <v>-1.987541568</v>
       </c>
       <c r="P87">
-        <v>-6.21968952</v>
+        <v>-6.293881632000001</v>
       </c>
       <c r="Q87">
-        <v>-6.33368952</v>
+        <v>-6.407881632</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3787693862117886</v>
+        <v>0.402552913798345</v>
       </c>
       <c r="T87">
-        <v>5.614342202546087</v>
+        <v>6.015366645585094</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.003297258719839302</v>
+        <v>0.003258918502166751</v>
       </c>
       <c r="W87">
-        <v>0.2350225063938619</v>
+        <v>0.2350315470171891</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.01373857799933054</v>
+        <v>0.01357882709236158</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8956,22 +8956,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2584845383665509</v>
+        <v>0.2603845383665509</v>
       </c>
       <c r="C88">
-        <v>-24.28303074461688</v>
+        <v>-24.77761363151478</v>
       </c>
       <c r="D88">
-        <v>9.100969255383122</v>
+        <v>9.020386368485234</v>
       </c>
       <c r="E88">
-        <v>29.80400000000001</v>
+        <v>30.21800000000001</v>
       </c>
       <c r="F88">
-        <v>35.60400000000001</v>
+        <v>36.01800000000001</v>
       </c>
       <c r="G88">
         <v>2.22</v>
@@ -8992,37 +8992,37 @@
         <v>0.114</v>
       </c>
       <c r="M88">
-        <v>8.395423200000002</v>
+        <v>8.493044400000002</v>
       </c>
       <c r="N88">
-        <v>-8.281423200000001</v>
+        <v>-8.379044400000002</v>
       </c>
       <c r="O88">
-        <v>-1.987541568</v>
+        <v>-2.010970656</v>
       </c>
       <c r="P88">
-        <v>-6.293881632000001</v>
+        <v>-6.368073744000001</v>
       </c>
       <c r="Q88">
-        <v>-6.407881632</v>
+        <v>-6.482073744000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.402552913798345</v>
+        <v>0.4299954456289869</v>
       </c>
       <c r="T88">
-        <v>6.015366645585094</v>
+        <v>6.478087156783948</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.003258918502166751</v>
+        <v>0.003221459668808512</v>
       </c>
       <c r="W88">
-        <v>0.2350315470171891</v>
+        <v>0.235040379810095</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.01357882709236158</v>
+        <v>0.01342274862003556</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9038,22 +9038,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2603845383665509</v>
+        <v>0.2622845383665509</v>
       </c>
       <c r="C89">
-        <v>-24.77761363151478</v>
+        <v>-25.2707820295419</v>
       </c>
       <c r="D89">
-        <v>9.020386368485234</v>
+        <v>8.941217970458105</v>
       </c>
       <c r="E89">
-        <v>30.21800000000001</v>
+        <v>30.632</v>
       </c>
       <c r="F89">
-        <v>36.01800000000001</v>
+        <v>36.432</v>
       </c>
       <c r="G89">
         <v>2.22</v>
@@ -9074,37 +9074,37 @@
         <v>0.114</v>
       </c>
       <c r="M89">
-        <v>8.493044400000002</v>
+        <v>8.590665600000001</v>
       </c>
       <c r="N89">
-        <v>-8.379044400000002</v>
+        <v>-8.4766656</v>
       </c>
       <c r="O89">
-        <v>-2.010970656</v>
+        <v>-2.034399744</v>
       </c>
       <c r="P89">
-        <v>-6.368073744000001</v>
+        <v>-6.442265856000001</v>
       </c>
       <c r="Q89">
-        <v>-6.482073744000001</v>
+        <v>-6.556265856</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4299954456289869</v>
+        <v>0.4620117327647358</v>
       </c>
       <c r="T89">
-        <v>6.478087156783948</v>
+        <v>7.017927753182611</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.003221459668808512</v>
+        <v>0.003184852172572053</v>
       </c>
       <c r="W89">
-        <v>0.235040379810095</v>
+        <v>0.2350490118577075</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.01342274862003556</v>
+        <v>0.01327021738571699</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9120,22 +9120,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2622845383665509</v>
+        <v>0.2641845383665509</v>
       </c>
       <c r="C90">
-        <v>-25.2707820295419</v>
+        <v>-25.7625728579171</v>
       </c>
       <c r="D90">
-        <v>8.941217970458105</v>
+        <v>8.8634271420829</v>
       </c>
       <c r="E90">
-        <v>30.632</v>
+        <v>31.046</v>
       </c>
       <c r="F90">
-        <v>36.432</v>
+        <v>36.846</v>
       </c>
       <c r="G90">
         <v>2.22</v>
@@ -9156,37 +9156,37 @@
         <v>0.114</v>
       </c>
       <c r="M90">
-        <v>8.590665600000001</v>
+        <v>8.688286800000002</v>
       </c>
       <c r="N90">
-        <v>-8.4766656</v>
+        <v>-8.574286800000001</v>
       </c>
       <c r="O90">
-        <v>-2.034399744</v>
+        <v>-2.057828832</v>
       </c>
       <c r="P90">
-        <v>-6.442265856000001</v>
+        <v>-6.516457968000001</v>
       </c>
       <c r="Q90">
-        <v>-6.556265856</v>
+        <v>-6.630457968000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4620117327647358</v>
+        <v>0.4998491630160755</v>
       </c>
       <c r="T90">
-        <v>7.017927753182611</v>
+        <v>7.65592118529012</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.003184852172572053</v>
+        <v>0.003149067316700456</v>
       </c>
       <c r="W90">
-        <v>0.2350490118577075</v>
+        <v>0.235057449926722</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.01327021738571699</v>
+        <v>0.01312111381958536</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9202,22 +9202,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2641845383665509</v>
+        <v>0.2660845383665509</v>
       </c>
       <c r="C91">
-        <v>-25.7625728579171</v>
+        <v>-26.25302176211543</v>
       </c>
       <c r="D91">
-        <v>8.8634271420829</v>
+        <v>8.786978237884574</v>
       </c>
       <c r="E91">
-        <v>31.046</v>
+        <v>31.46</v>
       </c>
       <c r="F91">
-        <v>36.846</v>
+        <v>37.26000000000001</v>
       </c>
       <c r="G91">
         <v>2.22</v>
@@ -9238,37 +9238,37 @@
         <v>0.114</v>
       </c>
       <c r="M91">
-        <v>8.688286800000002</v>
+        <v>8.785908000000001</v>
       </c>
       <c r="N91">
-        <v>-8.574286800000001</v>
+        <v>-8.671908</v>
       </c>
       <c r="O91">
-        <v>-2.057828832</v>
+        <v>-2.08125792</v>
       </c>
       <c r="P91">
-        <v>-6.516457968000001</v>
+        <v>-6.59065008</v>
       </c>
       <c r="Q91">
-        <v>-6.630457968000001</v>
+        <v>-6.70465008</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4998491630160755</v>
+        <v>0.5452540793176831</v>
       </c>
       <c r="T91">
-        <v>7.65592118529012</v>
+        <v>8.421513303819134</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.003149067316700456</v>
+        <v>0.003114077679848229</v>
       </c>
       <c r="W91">
-        <v>0.235057449926722</v>
+        <v>0.2350657004830918</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.01312111381958536</v>
+        <v>0.01297532366603438</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9284,22 +9284,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2660845383665509</v>
+        <v>0.2679845383665509</v>
       </c>
       <c r="C92">
-        <v>-26.25302176211543</v>
+        <v>-26.74216316832992</v>
       </c>
       <c r="D92">
-        <v>8.786978237884574</v>
+        <v>8.711836831670082</v>
       </c>
       <c r="E92">
-        <v>31.46</v>
+        <v>31.87400000000001</v>
       </c>
       <c r="F92">
-        <v>37.26000000000001</v>
+        <v>37.67400000000001</v>
       </c>
       <c r="G92">
         <v>2.22</v>
@@ -9320,37 +9320,37 @@
         <v>0.114</v>
       </c>
       <c r="M92">
-        <v>8.785908000000001</v>
+        <v>8.883529200000002</v>
       </c>
       <c r="N92">
-        <v>-8.671908</v>
+        <v>-8.769529200000001</v>
       </c>
       <c r="O92">
-        <v>-2.08125792</v>
+        <v>-2.104687008</v>
       </c>
       <c r="P92">
-        <v>-6.59065008</v>
+        <v>-6.664842192000001</v>
       </c>
       <c r="Q92">
-        <v>-6.70465008</v>
+        <v>-6.778842192000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5452540793176831</v>
+        <v>0.6007489770196479</v>
       </c>
       <c r="T92">
-        <v>8.421513303819134</v>
+        <v>9.357237004243483</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.003114077679848229</v>
+        <v>0.003079857046003743</v>
       </c>
       <c r="W92">
-        <v>0.2350657004830918</v>
+        <v>0.2350737697085523</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.01297532366603438</v>
+        <v>0.01283273769168236</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9366,22 +9366,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2679845383665509</v>
+        <v>0.2698845383665509</v>
       </c>
       <c r="C93">
-        <v>-26.74216316832992</v>
+        <v>-27.23003033516273</v>
       </c>
       <c r="D93">
-        <v>8.711836831670082</v>
+        <v>8.637969664837277</v>
       </c>
       <c r="E93">
-        <v>31.87400000000001</v>
+        <v>32.28800000000001</v>
       </c>
       <c r="F93">
-        <v>37.67400000000001</v>
+        <v>38.08800000000001</v>
       </c>
       <c r="G93">
         <v>2.22</v>
@@ -9402,37 +9402,37 @@
         <v>0.114</v>
       </c>
       <c r="M93">
-        <v>8.883529200000002</v>
+        <v>8.981150400000002</v>
       </c>
       <c r="N93">
-        <v>-8.769529200000001</v>
+        <v>-8.867150400000002</v>
       </c>
       <c r="O93">
-        <v>-2.104687008</v>
+        <v>-2.128116096</v>
       </c>
       <c r="P93">
-        <v>-6.664842192000001</v>
+        <v>-6.739034304000001</v>
       </c>
       <c r="Q93">
-        <v>-6.778842192000001</v>
+        <v>-6.853034304000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6007489770196479</v>
+        <v>0.670117599147104</v>
       </c>
       <c r="T93">
-        <v>9.357237004243483</v>
+        <v>10.52689162977392</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.003079857046003743</v>
+        <v>0.003046380338981963</v>
       </c>
       <c r="W93">
-        <v>0.2350737697085523</v>
+        <v>0.2350816635160681</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.01283273769168236</v>
+        <v>0.01269325141242494</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9448,22 +9448,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2698845383665509</v>
+        <v>0.2717845383665509</v>
       </c>
       <c r="C94">
-        <v>-27.23003033516273</v>
+        <v>-27.71665540270859</v>
       </c>
       <c r="D94">
-        <v>8.637969664837277</v>
+        <v>8.56534459729142</v>
       </c>
       <c r="E94">
-        <v>32.28800000000001</v>
+        <v>32.70200000000001</v>
       </c>
       <c r="F94">
-        <v>38.08800000000001</v>
+        <v>38.50200000000001</v>
       </c>
       <c r="G94">
         <v>2.22</v>
@@ -9484,37 +9484,37 @@
         <v>0.114</v>
       </c>
       <c r="M94">
-        <v>8.981150400000002</v>
+        <v>9.078771600000003</v>
       </c>
       <c r="N94">
-        <v>-8.867150400000002</v>
+        <v>-8.964771600000002</v>
       </c>
       <c r="O94">
-        <v>-2.128116096</v>
+        <v>-2.151545184000001</v>
       </c>
       <c r="P94">
-        <v>-6.739034304000001</v>
+        <v>-6.813226416000002</v>
       </c>
       <c r="Q94">
-        <v>-6.853034304000001</v>
+        <v>-6.927226416000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.670117599147104</v>
+        <v>0.7593058275966904</v>
       </c>
       <c r="T94">
-        <v>10.52689162977392</v>
+        <v>12.0307332911702</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.003046380338981963</v>
+        <v>0.003013623561143447</v>
       </c>
       <c r="W94">
-        <v>0.2350816635160681</v>
+        <v>0.2350893875642824</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.01269325141242494</v>
+        <v>0.01255676483809776</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9530,22 +9530,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2717845383665509</v>
+        <v>0.2736845383665509</v>
       </c>
       <c r="C95">
-        <v>-27.71665540270859</v>
+        <v>-28.20206943918296</v>
       </c>
       <c r="D95">
-        <v>8.56534459729142</v>
+        <v>8.493930560817049</v>
       </c>
       <c r="E95">
-        <v>32.70200000000001</v>
+        <v>33.11600000000001</v>
       </c>
       <c r="F95">
-        <v>38.50200000000001</v>
+        <v>38.91600000000001</v>
       </c>
       <c r="G95">
         <v>2.22</v>
@@ -9566,37 +9566,37 @@
         <v>0.114</v>
       </c>
       <c r="M95">
-        <v>9.078771600000003</v>
+        <v>9.176392800000002</v>
       </c>
       <c r="N95">
-        <v>-8.964771600000002</v>
+        <v>-9.062392800000001</v>
       </c>
       <c r="O95">
-        <v>-2.151545184000001</v>
+        <v>-2.174974272</v>
       </c>
       <c r="P95">
-        <v>-6.813226416000002</v>
+        <v>-6.887418528000001</v>
       </c>
       <c r="Q95">
-        <v>-6.927226416000002</v>
+        <v>-7.001418528000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7593058275966904</v>
+        <v>0.8782234655294723</v>
       </c>
       <c r="T95">
-        <v>12.0307332911702</v>
+        <v>14.03585550636523</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.003013623561143447</v>
+        <v>0.0029815637360249</v>
       </c>
       <c r="W95">
-        <v>0.2350893875642824</v>
+        <v>0.2350969472710454</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.01255676483809776</v>
+        <v>0.01242318223343719</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9612,22 +9612,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2736845383665509</v>
+        <v>0.2755845383665509</v>
       </c>
       <c r="C96">
-        <v>-28.20206943918296</v>
+        <v>-28.68630248523677</v>
       </c>
       <c r="D96">
-        <v>8.493930560817049</v>
+        <v>8.423697514763232</v>
       </c>
       <c r="E96">
-        <v>33.11600000000001</v>
+        <v>33.53</v>
       </c>
       <c r="F96">
-        <v>38.91600000000001</v>
+        <v>39.33000000000001</v>
       </c>
       <c r="G96">
         <v>2.22</v>
@@ -9648,37 +9648,37 @@
         <v>0.114</v>
       </c>
       <c r="M96">
-        <v>9.176392800000002</v>
+        <v>9.274014000000001</v>
       </c>
       <c r="N96">
-        <v>-9.062392800000001</v>
+        <v>-9.160014</v>
       </c>
       <c r="O96">
-        <v>-2.174974272</v>
+        <v>-2.19840336</v>
       </c>
       <c r="P96">
-        <v>-6.887418528000001</v>
+        <v>-6.96161064</v>
       </c>
       <c r="Q96">
-        <v>-7.001418528000001</v>
+        <v>-7.07561064</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8782234655294723</v>
+        <v>1.044708158635367</v>
       </c>
       <c r="T96">
-        <v>14.03585550636523</v>
+        <v>16.84302660763829</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0029815637360249</v>
+        <v>0.002950178854593059</v>
       </c>
       <c r="W96">
-        <v>0.2350969472710454</v>
+        <v>0.235104347826087</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.01242318223343719</v>
+        <v>0.01229241189413788</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9694,22 +9694,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2755845383665509</v>
+        <v>0.2774845383665509</v>
       </c>
       <c r="C97">
-        <v>-28.68630248523677</v>
+        <v>-29.16938359609074</v>
       </c>
       <c r="D97">
-        <v>8.423697514763232</v>
+        <v>8.354616403909265</v>
       </c>
       <c r="E97">
-        <v>33.53</v>
+        <v>33.944</v>
       </c>
       <c r="F97">
-        <v>39.33000000000001</v>
+        <v>39.74400000000001</v>
       </c>
       <c r="G97">
         <v>2.22</v>
@@ -9730,37 +9730,37 @@
         <v>0.114</v>
       </c>
       <c r="M97">
-        <v>9.274014000000001</v>
+        <v>9.371635200000002</v>
       </c>
       <c r="N97">
-        <v>-9.160014</v>
+        <v>-9.257635200000001</v>
       </c>
       <c r="O97">
-        <v>-2.19840336</v>
+        <v>-2.221832448</v>
       </c>
       <c r="P97">
-        <v>-6.96161064</v>
+        <v>-7.035802752</v>
       </c>
       <c r="Q97">
-        <v>-7.07561064</v>
+        <v>-7.149802752</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.044708158635367</v>
+        <v>1.29443519829421</v>
       </c>
       <c r="T97">
-        <v>16.84302660763829</v>
+        <v>21.05378325954787</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.002950178854593059</v>
+        <v>0.002919447824857715</v>
       </c>
       <c r="W97">
-        <v>0.235104347826087</v>
+        <v>0.2351115942028985</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.01229241189413788</v>
+        <v>0.01216436593690717</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9776,22 +9776,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2774845383665509</v>
+        <v>0.2793845383665509</v>
       </c>
       <c r="C98">
-        <v>-29.16938359609074</v>
+        <v>-29.65134088161328</v>
       </c>
       <c r="D98">
-        <v>8.354616403909265</v>
+        <v>8.286659118386723</v>
       </c>
       <c r="E98">
-        <v>33.944</v>
+        <v>34.358</v>
       </c>
       <c r="F98">
-        <v>39.74400000000001</v>
+        <v>40.158</v>
       </c>
       <c r="G98">
         <v>2.22</v>
@@ -9812,37 +9812,37 @@
         <v>0.114</v>
       </c>
       <c r="M98">
-        <v>9.371635200000002</v>
+        <v>9.469256400000001</v>
       </c>
       <c r="N98">
-        <v>-9.257635200000001</v>
+        <v>-9.3552564</v>
       </c>
       <c r="O98">
-        <v>-2.221832448</v>
+        <v>-2.245261536</v>
       </c>
       <c r="P98">
-        <v>-7.035802752</v>
+        <v>-7.109994864</v>
       </c>
       <c r="Q98">
-        <v>-7.149802752</v>
+        <v>-7.223994864</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.294435198294207</v>
+        <v>1.710646931058942</v>
       </c>
       <c r="T98">
-        <v>21.05378325954781</v>
+        <v>28.07171101273042</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.002919447824857715</v>
+        <v>0.00288935042460145</v>
       </c>
       <c r="W98">
-        <v>0.2351115942028985</v>
+        <v>0.235118691169879</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.01216436593690717</v>
+        <v>0.01203896010250616</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9858,22 +9858,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2793845383665509</v>
+        <v>0.2812845383665509</v>
       </c>
       <c r="C99">
-        <v>-29.65134088161328</v>
+        <v>-30.13220154445827</v>
       </c>
       <c r="D99">
-        <v>8.286659118386723</v>
+        <v>8.21979845554173</v>
       </c>
       <c r="E99">
-        <v>34.358</v>
+        <v>34.77200000000001</v>
       </c>
       <c r="F99">
-        <v>40.158</v>
+        <v>40.572</v>
       </c>
       <c r="G99">
         <v>2.22</v>
@@ -9894,37 +9894,37 @@
         <v>0.114</v>
       </c>
       <c r="M99">
-        <v>9.469256400000001</v>
+        <v>9.566877600000002</v>
       </c>
       <c r="N99">
-        <v>-9.3552564</v>
+        <v>-9.452877600000001</v>
       </c>
       <c r="O99">
-        <v>-2.245261536</v>
+        <v>-2.268690624</v>
       </c>
       <c r="P99">
-        <v>-7.109994864</v>
+        <v>-7.184186976000001</v>
       </c>
       <c r="Q99">
-        <v>-7.223994864</v>
+        <v>-7.298186976000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.710646931058942</v>
+        <v>2.543070396588413</v>
       </c>
       <c r="T99">
-        <v>28.07171101273042</v>
+        <v>42.10756651909563</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.00288935042460145</v>
+        <v>0.002859867257003476</v>
       </c>
       <c r="W99">
-        <v>0.235118691169879</v>
+        <v>0.2351256433007986</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.01203896010250616</v>
+        <v>0.01191611357084787</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9940,22 +9940,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2812845383665509</v>
+        <v>0.2831845383665509</v>
       </c>
       <c r="C100">
-        <v>-30.13220154445827</v>
+        <v>-30.61199191637127</v>
       </c>
       <c r="D100">
-        <v>8.21979845554173</v>
+        <v>8.154008083628737</v>
       </c>
       <c r="E100">
-        <v>34.77200000000001</v>
+        <v>35.18600000000001</v>
       </c>
       <c r="F100">
-        <v>40.572</v>
+        <v>40.986</v>
       </c>
       <c r="G100">
         <v>2.22</v>
@@ -9976,37 +9976,37 @@
         <v>0.114</v>
       </c>
       <c r="M100">
-        <v>9.566877600000002</v>
+        <v>9.664498800000001</v>
       </c>
       <c r="N100">
-        <v>-9.452877600000001</v>
+        <v>-9.5504988</v>
       </c>
       <c r="O100">
-        <v>-2.268690624</v>
+        <v>-2.292119712</v>
       </c>
       <c r="P100">
-        <v>-7.184186976000001</v>
+        <v>-7.258379088</v>
       </c>
       <c r="Q100">
-        <v>-7.298186976000001</v>
+        <v>-7.372379088</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.543070396588413</v>
+        <v>5.040340793176826</v>
       </c>
       <c r="T100">
-        <v>42.10756651909563</v>
+        <v>84.21513303819125</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.002859867257003476</v>
+        <v>0.002830979708952936</v>
       </c>
       <c r="W100">
-        <v>0.2351256433007986</v>
+        <v>0.2351324549846289</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10014,91 +10014,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.01191611357084787</v>
+        <v>0.01179574878730394</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2831845383665509</v>
-      </c>
-      <c r="C101">
-        <v>-30.61199191637127</v>
-      </c>
-      <c r="D101">
-        <v>8.154008083628737</v>
-      </c>
-      <c r="E101">
-        <v>35.18600000000001</v>
-      </c>
-      <c r="F101">
-        <v>40.986</v>
-      </c>
-      <c r="G101">
-        <v>2.22</v>
-      </c>
-      <c r="H101">
-        <v>35.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>-0.114</v>
-      </c>
-      <c r="L101">
-        <v>0.114</v>
-      </c>
-      <c r="M101">
-        <v>9.664498800000001</v>
-      </c>
-      <c r="N101">
-        <v>-9.5504988</v>
-      </c>
-      <c r="O101">
-        <v>-2.292119712</v>
-      </c>
-      <c r="P101">
-        <v>-7.258379088</v>
-      </c>
-      <c r="Q101">
-        <v>-7.372379088</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.040340793176826</v>
-      </c>
-      <c r="T101">
-        <v>84.21513303819125</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.002830979708952936</v>
-      </c>
-      <c r="W101">
-        <v>0.2351324549846289</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.01179574878730394</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
